--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -1191,7 +1191,7 @@
         <v>9</v>
       </c>
       <c r="G33">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34">
@@ -1322,26 +1322,51 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>09/04/26</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>9</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B39">
-        <v>14</v>
-      </c>
-      <c r="C39">
+      <c r="B40">
+        <v>30</v>
+      </c>
+      <c r="C40">
         <v>62</v>
       </c>
-      <c r="D39">
+      <c r="D40">
         <v>55</v>
       </c>
-      <c r="E39">
+      <c r="E40">
         <v>79</v>
       </c>
-      <c r="F39">
+      <c r="F40">
         <v>34</v>
       </c>
-      <c r="G39">
-        <v>244</v>
+      <c r="G40">
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -1351,7 +1376,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AM14"/>
+  <dimension ref="A1:AN14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1547,6 +1572,11 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>09/04/26</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1651,7 +1681,7 @@
         <v>1</v>
       </c>
       <c r="AG2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AH2">
         <v>7</v>
@@ -1669,7 +1699,10 @@
         <v>10</v>
       </c>
       <c r="AM2">
-        <v>244</v>
+        <v>9</v>
+      </c>
+      <c r="AN2">
+        <v>260</v>
       </c>
     </row>
     <row r="3">
@@ -1772,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -1790,7 +1823,10 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1911,6 +1947,9 @@
         <v>0</v>
       </c>
       <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
         <v>1</v>
       </c>
     </row>
@@ -2034,6 +2073,9 @@
       <c r="AM5">
         <v>0</v>
       </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2155,6 +2197,9 @@
       <c r="AM6">
         <v>0</v>
       </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2274,6 +2319,9 @@
         <v>2</v>
       </c>
       <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
         <v>16</v>
       </c>
     </row>
@@ -2395,6 +2443,9 @@
         <v>0</v>
       </c>
       <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
         <v>1</v>
       </c>
     </row>
@@ -2518,6 +2569,9 @@
       <c r="AM9">
         <v>0</v>
       </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2639,6 +2693,9 @@
       <c r="AM10">
         <v>0</v>
       </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2740,7 +2797,7 @@
         <v>0</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH11">
         <v>1</v>
@@ -2758,7 +2815,10 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -2861,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH12">
         <v>0</v>
@@ -2879,7 +2939,10 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -3000,7 +3063,10 @@
         <v>1</v>
       </c>
       <c r="AM13">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="AN13">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -3103,7 +3169,7 @@
         <v>1</v>
       </c>
       <c r="AG14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AH14">
         <v>8</v>
@@ -3121,7 +3187,10 @@
         <v>13</v>
       </c>
       <c r="AM14">
-        <v>276</v>
+        <v>10</v>
+      </c>
+      <c r="AN14">
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -3178,7 +3247,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C2">
         <v>62</v>
@@ -3193,7 +3262,7 @@
         <v>34</v>
       </c>
       <c r="G2">
-        <v>244</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3">
@@ -3203,7 +3272,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -3218,7 +3287,7 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -3403,7 +3472,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -3418,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -3428,7 +3497,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -3443,7 +3512,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -3453,7 +3522,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -3468,7 +3537,7 @@
         <v>2</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -3478,7 +3547,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C14">
         <v>71</v>
@@ -3493,7 +3562,7 @@
         <v>43</v>
       </c>
       <c r="G14">
-        <v>276</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -3503,7 +3572,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D285"/>
+  <dimension ref="A1:D305"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -9736,6 +9805,446 @@
         </is>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>10256</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>09/04/26</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Other Disposition (Please Describe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>10535</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Ineligible - Drive Through / Gas Kiosk</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>09/04/26</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>10037</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>09/04/26</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Eligible, Asked to Leave Before Audit Started - Permission Not Given</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>10651</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>10138</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>10037</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>09/04/26</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>10274</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>10135</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>10276</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>09/04/26</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>10005</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>10413</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>09/04/26</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>10278</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>10139</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>10134</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>10215</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>09/04/26</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>10280</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>09/04/26</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>10031</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>09/04/26</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>10077</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>09/04/26</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1399,26 +1399,51 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>09/18/26</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>8</v>
+      </c>
+      <c r="G42">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B42">
+      <c r="B43">
         <v>30</v>
       </c>
-      <c r="C42">
+      <c r="C43">
         <v>72</v>
       </c>
-      <c r="D42">
+      <c r="D43">
         <v>55</v>
       </c>
-      <c r="E42">
+      <c r="E43">
         <v>79</v>
       </c>
-      <c r="F42">
-        <v>39</v>
-      </c>
-      <c r="G42">
-        <v>275</v>
+      <c r="F43">
+        <v>47</v>
+      </c>
+      <c r="G43">
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -1428,7 +1453,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AP14"/>
+  <dimension ref="A1:AQ14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1639,6 +1664,11 @@
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
+          <t>09/18/26</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1770,7 +1800,10 @@
         <v>7</v>
       </c>
       <c r="AP2">
-        <v>275</v>
+        <v>8</v>
+      </c>
+      <c r="AQ2">
+        <v>283</v>
       </c>
     </row>
     <row r="3">
@@ -1900,6 +1933,9 @@
         <v>0</v>
       </c>
       <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
         <v>3</v>
       </c>
     </row>
@@ -2030,6 +2066,9 @@
         <v>0</v>
       </c>
       <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
         <v>1</v>
       </c>
     </row>
@@ -2162,6 +2201,9 @@
       <c r="AP5">
         <v>0</v>
       </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2292,6 +2334,9 @@
       <c r="AP6">
         <v>0</v>
       </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2420,6 +2465,9 @@
         <v>0</v>
       </c>
       <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
         <v>18</v>
       </c>
     </row>
@@ -2550,6 +2598,9 @@
         <v>0</v>
       </c>
       <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
         <v>1</v>
       </c>
     </row>
@@ -2680,7 +2731,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AQ9">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -2812,6 +2866,9 @@
       <c r="AP10">
         <v>0</v>
       </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2940,6 +2997,9 @@
         <v>0</v>
       </c>
       <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
         <v>8</v>
       </c>
     </row>
@@ -3070,6 +3130,9 @@
         <v>0</v>
       </c>
       <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
         <v>3</v>
       </c>
     </row>
@@ -3200,6 +3263,9 @@
         <v>0</v>
       </c>
       <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
         <v>4</v>
       </c>
     </row>
@@ -3330,7 +3396,10 @@
         <v>7</v>
       </c>
       <c r="AP14">
-        <v>313</v>
+        <v>9</v>
+      </c>
+      <c r="AQ14">
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -3399,10 +3468,10 @@
         <v>79</v>
       </c>
       <c r="F2">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G2">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3">
@@ -3562,7 +3631,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -3577,7 +3646,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3687,7 +3756,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14">
         <v>83</v>
@@ -3699,10 +3768,10 @@
         <v>84</v>
       </c>
       <c r="F14">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G14">
-        <v>313</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -3712,7 +3781,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D322"/>
+  <dimension ref="A1:D331"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -10754,6 +10823,204 @@
         </is>
       </c>
       <c r="D322" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>10009</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>09/18/26</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Review Needed, Store Not Found</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>10156</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>09/18/26</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>10041</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>09/18/26</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>10238</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>09/18/26</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>09/18/26</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>09/18/26</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>10259</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>09/18/26</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>10125</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>09/18/26</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>09/18/26</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
         <is>
           <t>Eligible, Audit Completed</t>
         </is>
@@ -11200,6 +11467,16 @@
           <t>9617 KY-30 W, Jackson, KY 41339</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>09/18/26</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Review Needed, Store Not Found</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12440,6 +12717,16 @@
           <t>6876 Lotts Creek Rd, Hazard, Kentucky, 41701</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>09/18/26</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -14195,11 +14482,6 @@
           <t>08/20/26</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Eligible, Audit Completed</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -14235,6 +14517,11 @@
           <t>08/20/26</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -14620,6 +14907,16 @@
           <t>350 Whitesburg Plaza, Whitesburg, KY 41858</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>09/18/26</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -14650,6 +14947,16 @@
           <t>35 Susan Cook Dr, Whitesburg, Kentucky, 41858</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>09/18/26</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -14720,6 +15027,16 @@
           <t>3433 Highway 119 N, Mayking, Kentucky, 41837</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>09/18/26</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -15430,6 +15747,16 @@
           <t>251 Medical Plaza Ln, Whitesburg, Kentucky, 41858</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>09/18/26</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -16515,6 +16842,16 @@
           <t>1766 Hwy 119 N, Ermine, KY 41815</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>09/18/26</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -18142,7 +18479,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>07/31/26</t>
+          <t>08/28/26</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -18182,7 +18519,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>08/28/26</t>
+          <t>07/31/26</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -18617,7 +18954,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>07/23/26</t>
+          <t>08/27/26</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -18657,7 +18994,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>08/27/26</t>
+          <t>07/23/26</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -19135,6 +19472,16 @@
           <t>6775 KY-7, Letcher, KY 41832</t>
         </is>
       </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>09/18/26</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -19805,6 +20152,16 @@
           <t>34 Whitesburg Plz, Whitesburg, Kentucky, 41858</t>
         </is>
       </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>09/18/26</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -20460,11 +20817,6 @@
           <t>07/20/26</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>Eligible, Audit Completed</t>
-        </is>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -20500,6 +20852,11 @@
           <t>07/20/26</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -21762,7 +22119,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>07/21/26</t>
+          <t>09/17/26</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -21842,7 +22199,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>09/17/26</t>
+          <t>07/21/26</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -24315,7 +24672,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -24383,7 +24740,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10009</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -24397,28 +24754,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dex Mini Mart</t>
+          <t>S C Turner Grocery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9617 KY-30 W, Jackson, KY 41339</t>
+          <t>15270 State Hwy 1110, Altro, KY 41339</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>10017</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AL-2</t>
+          <t>AL-3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -24427,23 +24784,23 @@
         </is>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S C Turner Grocery</t>
+          <t>Double Kwik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>15270 State Hwy 1110, Altro, KY 41339</t>
+          <t>931 N KY Highway 15, Hazard, Kentucky, 41701</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10017</t>
+          <t>10097</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -24457,23 +24814,23 @@
         </is>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Double Kwik</t>
+          <t>Fast Lane Discount Tobacco</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>931 N KY Highway 15, Hazard, Kentucky, 41701</t>
+          <t>373 Main St, Hazard, Kentucky, 41701</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>10141</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -24487,23 +24844,23 @@
         </is>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fast Lane Discount Tobacco</t>
+          <t>CLM Discount Tobacco</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>373 Main St, Hazard, Kentucky, 41701</t>
+          <t>208 W Ky Highway 80, Hazard, Kentucky, 41701</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -24517,28 +24874,28 @@
         </is>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CLM Discount Tobacco</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>208 W Ky Highway 80, Hazard, Kentucky, 41701</t>
+          <t>171 Citizens Ln, Hazard, Kentucky, 41701</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>10094</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AL-3</t>
+          <t>AL-4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -24547,7 +24904,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -24556,14 +24913,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>171 Citizens Ln, Hazard, Kentucky, 41701</t>
+          <t>400 Village Ln, Hazard, Kentucky, 41701</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10094</t>
+          <t>10657</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -24577,28 +24934,28 @@
         </is>
       </c>
       <c r="D9">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>Top of the Hill Liquors LLC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>400 Village Ln, Hazard, Kentucky, 41701</t>
+          <t>33 Boone Ridge Rd, Hazard, Kentucky, 41701</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>10138</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AL-4</t>
+          <t>AL-6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -24607,53 +24964,53 @@
         </is>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Top of the Hill Liquors LLC</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>33 Boone Ridge Rd, Hazard, Kentucky, 41701</t>
+          <t>21287 Highway 421, Hyden, Kentucky, 41749</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AL-6</t>
+          <t>CB-4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21287 Highway 421, Hyden, Kentucky, 41749</t>
+          <t>8380 US-23 N, Russell, Kentucky, 41169</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10025</t>
+          <t>10161</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -24667,33 +25024,33 @@
         </is>
       </c>
       <c r="D12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>Strictly Tobacco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>8380 US-23 N, Russell, Kentucky, 41169</t>
+          <t>1700 US Hwy 23, Russell, Kentucky, 41169</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>10279</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CB-4</t>
+          <t>JS-6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D13">
@@ -24701,29 +25058,29 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Strictly Tobacco</t>
+          <t>Marathon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1700 US Hwy 23, Russell, Kentucky, 41169</t>
+          <t>2100 State Route 3, Catlettsburg, Kentucky, 41129</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10279</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JS-6</t>
+          <t>NB-5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D14">
@@ -24731,24 +25088,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Marathon</t>
+          <t>Loves Travel Stop</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2100 State Route 3, Catlettsburg, Kentucky, 41129</t>
+          <t>750 N Carol Malone Blvd, Grayson, Kentucky, 41143</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NB-5</t>
+          <t>NB-7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -24757,53 +25114,53 @@
         </is>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Loves Travel Stop</t>
+          <t>KC Video &amp; Grocery</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>750 N Carol Malone Blvd, Grayson, Kentucky, 41143</t>
+          <t>9071 Highway 7 S, Kite, Kentucky, 41828</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>10145</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NB-7</t>
+          <t>SE-1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KC Video &amp; Grocery</t>
+          <t>Double Kwik</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>9071 Highway 7 S, Kite, Kentucky, 41828</t>
+          <t>2021 Highway 160 S, Hindman, Kentucky, 41822</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10145</t>
+          <t>10218</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -24817,23 +25174,23 @@
         </is>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Double Kwik</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2021 Highway 160 S, Hindman, Kentucky, 41822</t>
+          <t>100 Holly Hills Mall Rd, Hindman, Kentucky, 41822</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10218</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -24847,23 +25204,23 @@
         </is>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Hindman Quick Stop # 7</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>100 Holly Hills Mall Rd, Hindman, Kentucky, 41822</t>
+          <t>112 KY-899, Hindman, Kentucky, 41822</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -24877,28 +25234,28 @@
         </is>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hindman Quick Stop # 7</t>
+          <t>Fast Track</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>112 KY-899, Hindman, Kentucky, 41822</t>
+          <t>104 Highway 899, Hindman, Kentucky, 41822</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>10263</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SE-1</t>
+          <t>SE-2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -24907,23 +25264,23 @@
         </is>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fast Track</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>104 Highway 899, Hindman, Kentucky, 41822</t>
+          <t>32 Lost Creek Rd Dice, Hazard, KY 41722</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10263</t>
+          <t>10270</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -24937,23 +25294,23 @@
         </is>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>Double Kwik</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>32 Lost Creek Rd Dice, Hazard, KY 41722</t>
+          <t>28 KY-80, Hindman, Kentucky, 41822</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10270</t>
+          <t>10662</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -24967,28 +25324,28 @@
         </is>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Double Kwik</t>
+          <t>The Moon Spirits</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>28 KY-80, Hindman, Kentucky, 41822</t>
+          <t>388 Highway 80 E, Hindman, Kentucky, 41822</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SE-2</t>
+          <t>SE-4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -24997,28 +25354,28 @@
         </is>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>The Moon Spirits</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>388 Highway 80 E, Hindman, Kentucky, 41822</t>
+          <t>108 E Main St, Hazard, Kentucky, 41701</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10041</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SE-3</t>
+          <t>SE-6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -25027,286 +25384,16 @@
         </is>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lotts Creek Community Mart</t>
+          <t>Double Kwik</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>6876 Lotts Creek Rd, Hazard, Kentucky, 41701</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>10208</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>SE-4</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Shell</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>108 E Main St, Hazard, Kentucky, 41701</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>10106</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>SE-5</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>6</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Double Kwik</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>35 Susan Cook Dr, Whitesburg, Kentucky, 41858</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>10125</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>SE-5</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>9</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Food City</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>251 Medical Plaza Ln, Whitesburg, Kentucky, 41858</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>10105</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>SE-6</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Walmart</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>350 Whitesburg Plaza, Whitesburg, KY 41858</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>10108</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>SE-6</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>3</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Dollar General</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>3433 Highway 119 N, Mayking, Kentucky, 41837</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>10156</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>SE-6</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>2</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Exxon</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>1766 Hwy 119 N, Ermine, KY 41815</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>10196</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>SE-6</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>7</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Double Kwik</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
           <t>122 Jenkins Rd, Whitesburg, Kentucky, 41858</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>10238</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>SE-6</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Dollar General</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>6775 KY-7, Letcher, KY 41832</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>10259</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>SE-6</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D33">
-        <v>6</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Price Less Foods</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>34 Whitesburg Plz, Whitesburg, Kentucky, 41858</t>
         </is>
       </c>
     </row>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1449,26 +1449,51 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>09/23/26</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B44">
+      <c r="B45">
         <v>30</v>
       </c>
-      <c r="C44">
+      <c r="C45">
         <v>73</v>
       </c>
-      <c r="D44">
+      <c r="D45">
         <v>55</v>
       </c>
-      <c r="E44">
+      <c r="E45">
         <v>79</v>
       </c>
-      <c r="F44">
-        <v>47</v>
-      </c>
-      <c r="G44">
-        <v>284</v>
+      <c r="F45">
+        <v>48</v>
+      </c>
+      <c r="G45">
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -1478,7 +1503,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AR14"/>
+  <dimension ref="A1:AS14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1699,6 +1724,11 @@
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
+          <t>09/23/26</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1836,7 +1866,10 @@
         <v>1</v>
       </c>
       <c r="AR2">
-        <v>284</v>
+        <v>1</v>
+      </c>
+      <c r="AS2">
+        <v>285</v>
       </c>
     </row>
     <row r="3">
@@ -1972,6 +2005,9 @@
         <v>0</v>
       </c>
       <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
         <v>3</v>
       </c>
     </row>
@@ -2108,6 +2144,9 @@
         <v>0</v>
       </c>
       <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
         <v>1</v>
       </c>
     </row>
@@ -2246,6 +2285,9 @@
       <c r="AR5">
         <v>0</v>
       </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2382,6 +2424,9 @@
       <c r="AR6">
         <v>0</v>
       </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2516,6 +2561,9 @@
         <v>0</v>
       </c>
       <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
         <v>18</v>
       </c>
     </row>
@@ -2652,6 +2700,9 @@
         <v>0</v>
       </c>
       <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
         <v>1</v>
       </c>
     </row>
@@ -2788,6 +2839,9 @@
         <v>0</v>
       </c>
       <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
         <v>1</v>
       </c>
     </row>
@@ -2926,6 +2980,9 @@
       <c r="AR10">
         <v>0</v>
       </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3060,6 +3117,9 @@
         <v>0</v>
       </c>
       <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
         <v>8</v>
       </c>
     </row>
@@ -3196,6 +3256,9 @@
         <v>0</v>
       </c>
       <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
         <v>3</v>
       </c>
     </row>
@@ -3332,6 +3395,9 @@
         <v>0</v>
       </c>
       <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
         <v>4</v>
       </c>
     </row>
@@ -3468,7 +3534,10 @@
         <v>1</v>
       </c>
       <c r="AR14">
-        <v>323</v>
+        <v>1</v>
+      </c>
+      <c r="AS14">
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -3537,10 +3606,10 @@
         <v>79</v>
       </c>
       <c r="F2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G2">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3">
@@ -3837,10 +3906,10 @@
         <v>84</v>
       </c>
       <c r="F14">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G14">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -3850,7 +3919,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D332"/>
+  <dimension ref="A1:D333"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -11112,6 +11181,28 @@
         </is>
       </c>
       <c r="D332" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>10196</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>09/23/26</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
         <is>
           <t>Eligible, Audit Completed</t>
         </is>
@@ -18188,6 +18279,16 @@
           <t>122 Jenkins Rd, Whitesburg, Kentucky, 41858</t>
         </is>
       </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>09/23/26</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -24803,7 +24904,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -25498,36 +25599,6 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>10196</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>SE-6</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>7</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Double Kwik</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>122 Jenkins Rd, Whitesburg, Kentucky, 41858</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1474,26 +1474,51 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>09/24/26</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>4</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B45">
+      <c r="B46">
         <v>30</v>
       </c>
-      <c r="C45">
+      <c r="C46">
         <v>73</v>
       </c>
-      <c r="D45">
+      <c r="D46">
         <v>55</v>
       </c>
-      <c r="E45">
-        <v>79</v>
-      </c>
-      <c r="F45">
+      <c r="E46">
+        <v>83</v>
+      </c>
+      <c r="F46">
         <v>48</v>
       </c>
-      <c r="G45">
-        <v>285</v>
+      <c r="G46">
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -1503,7 +1528,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AS14"/>
+  <dimension ref="A1:AT14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1729,6 +1754,11 @@
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
+          <t>09/24/26</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1869,7 +1899,10 @@
         <v>1</v>
       </c>
       <c r="AS2">
-        <v>285</v>
+        <v>4</v>
+      </c>
+      <c r="AT2">
+        <v>289</v>
       </c>
     </row>
     <row r="3">
@@ -2008,6 +2041,9 @@
         <v>0</v>
       </c>
       <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
         <v>3</v>
       </c>
     </row>
@@ -2147,6 +2183,9 @@
         <v>0</v>
       </c>
       <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
         <v>1</v>
       </c>
     </row>
@@ -2288,6 +2327,9 @@
       <c r="AS5">
         <v>0</v>
       </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2427,6 +2469,9 @@
       <c r="AS6">
         <v>0</v>
       </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2564,6 +2609,9 @@
         <v>0</v>
       </c>
       <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
         <v>18</v>
       </c>
     </row>
@@ -2703,6 +2751,9 @@
         <v>0</v>
       </c>
       <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
         <v>1</v>
       </c>
     </row>
@@ -2842,6 +2893,9 @@
         <v>0</v>
       </c>
       <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
         <v>1</v>
       </c>
     </row>
@@ -2983,6 +3037,9 @@
       <c r="AS10">
         <v>0</v>
       </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3120,6 +3177,9 @@
         <v>0</v>
       </c>
       <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
         <v>8</v>
       </c>
     </row>
@@ -3259,6 +3319,9 @@
         <v>0</v>
       </c>
       <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
         <v>3</v>
       </c>
     </row>
@@ -3398,7 +3461,10 @@
         <v>0</v>
       </c>
       <c r="AS13">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="AT13">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -3537,7 +3603,10 @@
         <v>1</v>
       </c>
       <c r="AS14">
-        <v>324</v>
+        <v>5</v>
+      </c>
+      <c r="AT14">
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -3603,13 +3672,13 @@
         <v>55</v>
       </c>
       <c r="E2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F2">
         <v>48</v>
       </c>
       <c r="G2">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3">
@@ -3878,13 +3947,13 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13">
         <v>2</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -3903,13 +3972,13 @@
         <v>64</v>
       </c>
       <c r="E14">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F14">
         <v>57</v>
       </c>
       <c r="G14">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -3919,7 +3988,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D333"/>
+  <dimension ref="A1:D338"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -11203,6 +11272,116 @@
         </is>
       </c>
       <c r="D333" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>10017</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>09/24/26</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>10160</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>09/24/26</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>10141</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>09/24/26</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Other Disposition (Please Describe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>10657</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>09/24/26</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>10020</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>09/24/26</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
         <is>
           <t>Eligible, Audit Completed</t>
         </is>
@@ -11929,6 +12108,16 @@
           <t>931 N KY Highway 15, Hazard, Kentucky, 41701</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>09/24/26</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11999,6 +12188,16 @@
           <t>9071 Highway 7 S, Kite, Kentucky, 41828</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>09/24/26</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -12581,7 +12780,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>07/29/26</t>
+          <t>09/22/26</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -12621,7 +12820,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>09/22/26</t>
+          <t>07/29/26</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -14461,12 +14660,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>08/07/26</t>
+          <t>08/31/26</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
+          <t>Not Attempted, Permanently Closed</t>
         </is>
       </c>
     </row>
@@ -14501,12 +14700,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>08/31/26</t>
+          <t>08/07/26</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Not Attempted, Permanently Closed</t>
+          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
         </is>
       </c>
     </row>
@@ -15411,12 +15610,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>07/22/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Other Disposition (Please Describe)</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
@@ -15451,12 +15650,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>07/22/26</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Other Disposition (Please Describe)</t>
         </is>
       </c>
     </row>
@@ -16494,11 +16693,6 @@
           <t>08/26/26</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Eligible, Audit Completed</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -16574,6 +16768,11 @@
           <t>08/26/26</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -16684,6 +16883,16 @@
           <t>208 W Ky Highway 80, Hazard, Kentucky, 41701</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>09/24/26</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Other Disposition (Please Describe)</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -17184,6 +17393,16 @@
           <t>171 Citizens Ln, Hazard, Kentucky, 41701</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>09/24/26</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -17256,12 +17475,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>08/28/26</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Eligible, Audit Completed</t>
+          <t>08/31/26</t>
         </is>
       </c>
     </row>
@@ -17296,7 +17510,12 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>08/31/26</t>
+          <t>08/28/26</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
@@ -18711,7 +18930,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>08/28/26</t>
+          <t>07/31/26</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -18751,7 +18970,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>07/31/26</t>
+          <t>08/28/26</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -20576,7 +20795,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>08/27/26</t>
+          <t>08/31/26</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -20616,7 +20835,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>08/31/26</t>
+          <t>08/27/26</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -21049,6 +21268,11 @@
           <t>07/20/26</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -21084,11 +21308,6 @@
           <t>07/20/26</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>Eligible, Audit Completed</t>
-        </is>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -21441,7 +21660,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>07/28/26</t>
+          <t>08/31/26</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -21481,7 +21700,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>08/31/26</t>
+          <t>07/28/26</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -21561,12 +21780,12 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>07/22/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Re-Attempt Needed, Temporarily Closed</t>
+          <t>Eligible, Asked to Leave Before Audit Started - Permission Not Given</t>
         </is>
       </c>
     </row>
@@ -21601,12 +21820,12 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>07/22/26</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Eligible, Asked to Leave Before Audit Started - Permission Not Given</t>
+          <t>Re-Attempt Needed, Temporarily Closed</t>
         </is>
       </c>
     </row>
@@ -22351,7 +22570,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>09/17/26</t>
+          <t>07/21/26</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -22391,7 +22610,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>07/21/26</t>
+          <t>09/17/26</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -24327,6 +24546,16 @@
       <c r="F332" t="inlineStr">
         <is>
           <t>33 Boone Ridge Rd, Hazard, Kentucky, 41701</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>09/24/26</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
@@ -24904,7 +25133,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -25002,7 +25231,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10017</t>
+          <t>10097</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -25016,28 +25245,28 @@
         </is>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Double Kwik</t>
+          <t>Fast Lane Discount Tobacco</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>931 N KY Highway 15, Hazard, Kentucky, 41701</t>
+          <t>373 Main St, Hazard, Kentucky, 41701</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>10094</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AL-3</t>
+          <t>AL-4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -25046,28 +25275,28 @@
         </is>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fast Lane Discount Tobacco</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>373 Main St, Hazard, Kentucky, 41701</t>
+          <t>400 Village Ln, Hazard, Kentucky, 41701</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>10138</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AL-3</t>
+          <t>AL-6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -25076,37 +25305,37 @@
         </is>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CLM Discount Tobacco</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>208 W Ky Highway 80, Hazard, Kentucky, 41701</t>
+          <t>21287 Highway 421, Hyden, Kentucky, 41749</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AL-3</t>
+          <t>CB-4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -25115,259 +25344,259 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>171 Citizens Ln, Hazard, Kentucky, 41701</t>
+          <t>8380 US-23 N, Russell, Kentucky, 41169</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10094</t>
+          <t>10161</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AL-4</t>
+          <t>CB-4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>Strictly Tobacco</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>400 Village Ln, Hazard, Kentucky, 41701</t>
+          <t>1700 US Hwy 23, Russell, Kentucky, 41169</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>10279</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AL-4</t>
+          <t>JS-6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Top of the Hill Liquors LLC</t>
+          <t>Marathon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>33 Boone Ridge Rd, Hazard, Kentucky, 41701</t>
+          <t>2100 State Route 3, Catlettsburg, Kentucky, 41129</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AL-6</t>
+          <t>NB-5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Loves Travel Stop</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21287 Highway 421, Hyden, Kentucky, 41749</t>
+          <t>750 N Carol Malone Blvd, Grayson, Kentucky, 41143</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10025</t>
+          <t>10145</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CB-4</t>
+          <t>SE-1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D11">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>Double Kwik</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>8380 US-23 N, Russell, Kentucky, 41169</t>
+          <t>2021 Highway 160 S, Hindman, Kentucky, 41822</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>10218</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CB-4</t>
+          <t>SE-1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Strictly Tobacco</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1700 US Hwy 23, Russell, Kentucky, 41169</t>
+          <t>100 Holly Hills Mall Rd, Hindman, Kentucky, 41822</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10279</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JS-6</t>
+          <t>SE-1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Marathon</t>
+          <t>Hindman Quick Stop # 7</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2100 State Route 3, Catlettsburg, Kentucky, 41129</t>
+          <t>112 KY-899, Hindman, Kentucky, 41822</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NB-5</t>
+          <t>SE-1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Loves Travel Stop</t>
+          <t>Fast Track</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>750 N Carol Malone Blvd, Grayson, Kentucky, 41143</t>
+          <t>104 Highway 899, Hindman, Kentucky, 41822</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>10263</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NB-7</t>
+          <t>SE-2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KC Video &amp; Grocery</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>9071 Highway 7 S, Kite, Kentucky, 41828</t>
+          <t>32 Lost Creek Rd Dice, Hazard, KY 41722</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10145</t>
+          <t>10270</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SE-1</t>
+          <t>SE-2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -25376,7 +25605,7 @@
         </is>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -25385,19 +25614,19 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2021 Highway 160 S, Hindman, Kentucky, 41822</t>
+          <t>28 KY-80, Hindman, Kentucky, 41822</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10218</t>
+          <t>10662</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SE-1</t>
+          <t>SE-2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -25406,28 +25635,28 @@
         </is>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>The Moon Spirits</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>100 Holly Hills Mall Rd, Hindman, Kentucky, 41822</t>
+          <t>388 Highway 80 E, Hindman, Kentucky, 41822</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SE-1</t>
+          <t>SE-4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -25436,164 +25665,14 @@
         </is>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hindman Quick Stop # 7</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
-        <is>
-          <t>112 KY-899, Hindman, Kentucky, 41822</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>10650</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>SE-1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Fast Track</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>104 Highway 899, Hindman, Kentucky, 41822</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>10263</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>SE-2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>BP</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>32 Lost Creek Rd Dice, Hazard, KY 41722</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>10270</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SE-2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>6</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Double Kwik</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>28 KY-80, Hindman, Kentucky, 41822</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>10662</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SE-2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>5</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>The Moon Spirits</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>388 Highway 80 E, Hindman, Kentucky, 41822</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>10208</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>SE-4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Shell</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
         <is>
           <t>108 E Main St, Hazard, Kentucky, 41701</t>
         </is>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -1528,7 +1528,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AT14"/>
+  <dimension ref="A1:AU14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1759,6 +1759,11 @@
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
+          <t>09/25/26</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1902,6 +1907,9 @@
         <v>4</v>
       </c>
       <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
         <v>289</v>
       </c>
     </row>
@@ -2044,6 +2052,9 @@
         <v>0</v>
       </c>
       <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
         <v>3</v>
       </c>
     </row>
@@ -2186,6 +2197,9 @@
         <v>0</v>
       </c>
       <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
         <v>1</v>
       </c>
     </row>
@@ -2330,6 +2344,9 @@
       <c r="AT5">
         <v>0</v>
       </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2472,6 +2489,9 @@
       <c r="AT6">
         <v>0</v>
       </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2612,6 +2632,9 @@
         <v>0</v>
       </c>
       <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
         <v>18</v>
       </c>
     </row>
@@ -2754,6 +2777,9 @@
         <v>0</v>
       </c>
       <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
         <v>1</v>
       </c>
     </row>
@@ -2898,6 +2924,9 @@
       <c r="AT9">
         <v>1</v>
       </c>
+      <c r="AU9">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3040,6 +3069,9 @@
       <c r="AT10">
         <v>0</v>
       </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3180,6 +3212,9 @@
         <v>0</v>
       </c>
       <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
         <v>8</v>
       </c>
     </row>
@@ -3322,6 +3357,9 @@
         <v>0</v>
       </c>
       <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
         <v>3</v>
       </c>
     </row>
@@ -3461,10 +3499,13 @@
         <v>0</v>
       </c>
       <c r="AS13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -3603,9 +3644,12 @@
         <v>1</v>
       </c>
       <c r="AS14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT14">
+        <v>1</v>
+      </c>
+      <c r="AU14">
         <v>329</v>
       </c>
     </row>
@@ -3847,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -3947,13 +3991,13 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>2</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -11324,7 +11368,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>10657</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -11339,14 +11383,14 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Other Disposition (Please Describe)</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -11368,12 +11412,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>10141</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>09/24/26</t>
+          <t>09/25/26</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -11383,7 +11427,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Review Needed, Store Not Found</t>
         </is>
       </c>
     </row>
@@ -12780,7 +12824,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>09/22/26</t>
+          <t>07/29/26</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -12820,7 +12864,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>07/29/26</t>
+          <t>09/22/26</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -15058,6 +15102,11 @@
           <t>08/28/26</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -15093,11 +15142,6 @@
           <t>08/28/26</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Eligible, Audit Completed</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -16885,12 +16929,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>09/24/26</t>
+          <t>09/25/26</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Other Disposition (Please Describe)</t>
+          <t>Review Needed, Store Not Found</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18974,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>07/31/26</t>
+          <t>08/28/26</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -18970,7 +19014,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>08/28/26</t>
+          <t>07/31/26</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -19330,12 +19374,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>08/26/26</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Eligible, Audit Completed</t>
+          <t>07/22/26</t>
         </is>
       </c>
     </row>
@@ -19370,7 +19409,12 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>07/22/26</t>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
@@ -19405,7 +19449,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>08/27/26</t>
+          <t>07/23/26</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -19445,7 +19489,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>07/23/26</t>
+          <t>08/27/26</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -20795,7 +20839,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>08/31/26</t>
+          <t>08/27/26</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -20835,7 +20879,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>08/27/26</t>
+          <t>08/31/26</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -21268,11 +21312,6 @@
           <t>07/20/26</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Eligible, Audit Completed</t>
-        </is>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -21308,6 +21347,11 @@
           <t>07/20/26</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -21340,7 +21384,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>09/04/26</t>
+          <t>08/29/26</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -21380,7 +21424,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>08/29/26</t>
+          <t>09/04/26</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -1528,7 +1528,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU14"/>
+  <dimension ref="A1:AV14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1764,6 +1764,11 @@
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
+          <t>09/30/26</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1910,6 +1915,9 @@
         <v>0</v>
       </c>
       <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
         <v>289</v>
       </c>
     </row>
@@ -2055,7 +2063,10 @@
         <v>0</v>
       </c>
       <c r="AU3">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="AV3">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2200,6 +2211,9 @@
         <v>0</v>
       </c>
       <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
         <v>1</v>
       </c>
     </row>
@@ -2347,6 +2361,9 @@
       <c r="AU5">
         <v>0</v>
       </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2492,6 +2509,9 @@
       <c r="AU6">
         <v>0</v>
       </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2635,6 +2655,9 @@
         <v>0</v>
       </c>
       <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
         <v>18</v>
       </c>
     </row>
@@ -2780,6 +2803,9 @@
         <v>0</v>
       </c>
       <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
         <v>1</v>
       </c>
     </row>
@@ -2925,6 +2951,9 @@
         <v>1</v>
       </c>
       <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
         <v>2</v>
       </c>
     </row>
@@ -3072,6 +3101,9 @@
       <c r="AU10">
         <v>0</v>
       </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3215,6 +3247,9 @@
         <v>0</v>
       </c>
       <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
         <v>8</v>
       </c>
     </row>
@@ -3360,6 +3395,9 @@
         <v>0</v>
       </c>
       <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
         <v>3</v>
       </c>
     </row>
@@ -3505,6 +3543,9 @@
         <v>0</v>
       </c>
       <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
         <v>4</v>
       </c>
     </row>
@@ -3650,7 +3691,10 @@
         <v>1</v>
       </c>
       <c r="AU14">
-        <v>329</v>
+        <v>1</v>
+      </c>
+      <c r="AV14">
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -3741,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -4016,13 +4060,13 @@
         <v>64</v>
       </c>
       <c r="E14">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F14">
         <v>57</v>
       </c>
       <c r="G14">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -4032,7 +4076,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D338"/>
+  <dimension ref="A1:D339"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -11428,6 +11472,28 @@
       <c r="D338" t="inlineStr">
         <is>
           <t>Review Needed, Store Not Found</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>10293</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>09/30/26</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Eligible, Asked to Leave Before Audit Started - Permission Not Given</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11504,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H347"/>
+  <dimension ref="A1:H348"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -21876,207 +21942,207 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>10293</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>JS-6</t>
+          <t>SE-1</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D264">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Smokin Toms</t>
+          <t>Double J Tobacco</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>12484 US Route 60, Ashland, Kentucky, 41102</t>
+          <t>1256 Highway 160 S, Hindman, Kentucky, 41822</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>08/24/26</t>
+          <t>09/30/26</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Eligible, Asked to Leave Before Audit Started - Permission Not Given</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>10294</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>NB-4</t>
+          <t>JS-6</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D265">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>The Eastern Kentucky Hemp Company</t>
+          <t>Smokin Toms</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>123 E Main St, Grayson, Kentucky, 41143</t>
+          <t>12484 US Route 60, Ashland, Kentucky, 41102</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>08/21/26</t>
+          <t>08/24/26</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Not Attempted, Permanently Closed</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>CB-4</t>
+          <t>NB-4</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D266">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Marathon</t>
+          <t>The Eastern Kentucky Hemp Company</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>11825 US 23 Hwy, Greenup, Kentucky, 41144</t>
+          <t>123 E Main St, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>08/24/26</t>
+          <t>08/21/26</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Not Attempted, Permanently Closed</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>SE-1</t>
+          <t>CB-4</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D267">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Hindman Quick Stop # 7</t>
+          <t>Marathon</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>112 KY-899, Hindman, Kentucky, 41822</t>
+          <t>11825 US 23 Hwy, Greenup, Kentucky, 41144</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>08/24/26</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>CB-3</t>
+          <t>SE-1</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D268">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Greenup Tobacco and Beer</t>
+          <t>Hindman Quick Stop # 7</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>1103 Seaton Ave, Greenup, Kentucky, 41144</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>08/19/26</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>Eligible, Audit Completed</t>
+          <t>112 KY-899, Hindman, Kentucky, 41822</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>JS-6</t>
+          <t>CB-3</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D269">
@@ -22084,17 +22150,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Exxon</t>
+          <t>Greenup Tobacco and Beer</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>10973 US Route 60, Ashland, Kentucky, 41102</t>
+          <t>1103 Seaton Ave, Greenup, Kentucky, 41144</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>08/24/26</t>
+          <t>08/19/26</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -22106,35 +22172,35 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>NB-2</t>
+          <t>JS-6</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D270">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Marathon</t>
+          <t>Exxon</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>1051 N State Highway 7, Grayson, Kentucky, 41143</t>
+          <t>10973 US Route 60, Ashland, Kentucky, 41102</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>07/22/26</t>
+          <t>08/24/26</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -22146,35 +22212,35 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>SE-7</t>
+          <t>NB-2</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D271">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Happy IGA</t>
+          <t>Marathon</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>10036 KY-15, Happy, Kentucky, 41746</t>
+          <t>1051 N State Highway 7, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>09/17/26</t>
+          <t>07/22/26</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -22186,35 +22252,35 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>CB-2</t>
+          <t>SE-7</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D272">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Happy IGA</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>10003 KY-7, South Shore, Kentucky, 41175</t>
+          <t>10036 KY-15, Happy, Kentucky, 41746</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>07/28/26</t>
+          <t>09/17/26</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -22254,7 +22320,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>08/31/26</t>
+          <t>07/28/26</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -22266,115 +22332,115 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>10309</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>SE-2</t>
+          <t>CB-2</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D274">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Cardinal Country Store</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>100 Jamestown Vlg, Hazard, Kentucky, 41701</t>
+          <t>10003 KY-7, South Shore, Kentucky, 41175</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>08/31/26</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Eligible, Asked to Leave During Audit - Audit Partially Complete</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>10310</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>AL-2</t>
+          <t>SE-2</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D275">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Nabels</t>
+          <t>Cardinal Country Store</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>3108 KY-28, Hazard, Kentucky, 41701</t>
+          <t>100 Jamestown Vlg, Hazard, Kentucky, 41701</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>08/18/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Eligible, Asked to Leave During Audit - Audit Partially Complete</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10310</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>JS-1</t>
+          <t>AL-2</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D276">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Ashland Beverage Centre</t>
+          <t>Nabels</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>744 Winchester Ave, Ashland, Kentucky, 41101</t>
+          <t>3108 KY-28, Hazard, Kentucky, 41701</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>07/18/26</t>
+          <t>08/18/26</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -22386,35 +22452,35 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10314</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>AL-7</t>
+          <t>JS-1</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D277">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Rocks Market</t>
+          <t>Ashland Beverage Centre</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>1571 Highway 421, Bledsoe, Kentucky, 40810</t>
+          <t>744 Winchester Ave, Ashland, Kentucky, 41101</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>08/12/26</t>
+          <t>07/18/26</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -22426,35 +22492,35 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>10327</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>SE-2</t>
+          <t>AL-7</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D278">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>The Honey Hole on East 80</t>
+          <t>Rocks Market</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>7934 E Ky Highway 80, Hazard, Kentucky, 41701</t>
+          <t>1571 Highway 421, Bledsoe, Kentucky, 40810</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>08/12/26</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -22466,12 +22532,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>SE-3</t>
+          <t>SE-2</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -22480,21 +22546,21 @@
         </is>
       </c>
       <c r="D279">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>IGA food world</t>
+          <t>The Honey Hole on East 80</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>3149 Highway 805, Neon, Kentucky, 41840</t>
+          <t>7934 E Ky Highway 80, Hazard, Kentucky, 41701</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>09/01/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -22506,115 +22572,115 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>10349</t>
+          <t>10342</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>CB-6</t>
+          <t>SE-3</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D280">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Alex's Smoke Shop</t>
+          <t>IGA food world</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>421 Russell Rd, Ashland, Kentucky, 41101</t>
+          <t>3149 Highway 805, Neon, Kentucky, 41840</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>08/28/26</t>
+          <t>09/01/26</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Not Attempted, Permanently Closed</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>SE-4</t>
+          <t>CB-6</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D281">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Cornetts Whiskey Store</t>
+          <t>Alex's Smoke Shop</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>11300 KY-7, Cornettsville, KY 41731</t>
+          <t>421 Russell Rd, Ashland, Kentucky, 41101</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>09/01/26</t>
+          <t>08/28/26</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Not Attempted, Permanently Closed</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10353</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>JS-4</t>
+          <t>SE-4</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D282">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Kroger</t>
+          <t>Cornetts Whiskey Store</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>711 Martin Luther King Jr Blvd, Ste 5, Ashland, Kentucky, 41101</t>
+          <t>11300 KY-7, Cornettsville, KY 41731</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>07/21/26</t>
+          <t>09/01/26</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -22654,7 +22720,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>09/17/26</t>
+          <t>07/21/26</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -22694,7 +22760,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>08/31/26</t>
+          <t>09/17/26</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -22706,35 +22772,35 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>10372</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>NB-2</t>
+          <t>JS-4</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D285">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Super Quik</t>
+          <t>Kroger</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>951 N Carol Malone Blvd, Grayson, Kentucky, 41143</t>
+          <t>711 Martin Luther King Jr Blvd, Ste 5, Ashland, Kentucky, 41101</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>07/22/26</t>
+          <t>08/31/26</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -22746,12 +22812,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>10384</t>
+          <t>10372</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>NB-6</t>
+          <t>NB-2</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -22760,21 +22826,21 @@
         </is>
       </c>
       <c r="D286">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Go Time</t>
+          <t>Super Quik</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>8354 Highway 15 S, Jackson, Kentucky, 41339</t>
+          <t>951 N Carol Malone Blvd, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>07/29/26</t>
+          <t>07/22/26</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -22786,35 +22852,35 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>10400</t>
+          <t>10384</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>CB-2</t>
+          <t>NB-6</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D287">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Go Time</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>27 Chicken Coop Rd, Grayson, Kentucky, 41143</t>
+          <t>8354 Highway 15 S, Jackson, Kentucky, 41339</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>07/20/26</t>
+          <t>07/29/26</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -22826,35 +22892,35 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10400</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>AL-1</t>
+          <t>CB-2</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D288">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Indian Hollow Liquors</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>241 Highway 15 S, Jackson, Kentucky, 41339</t>
+          <t>27 Chicken Coop Rd, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>09/04/26</t>
+          <t>07/20/26</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -22866,35 +22932,35 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>10453</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>NB-4</t>
+          <t>AL-1</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D289">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Clark's Pump-N-Shop</t>
+          <t>Indian Hollow Liquors</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>311 N Carol Malone Blvd, Grayson, Kentucky, 41143</t>
+          <t>241 Highway 15 S, Jackson, Kentucky, 41339</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>07/22/26</t>
+          <t>09/04/26</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -22906,97 +22972,97 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>10458</t>
+          <t>10453</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>SE-2</t>
+          <t>NB-4</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D290">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Southern Spirits Liquor Store</t>
+          <t>Clark's Pump-N-Shop</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>2815 N Main St, Hazard, Kentucky, 41701</t>
+          <t>311 N Carol Malone Blvd, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>07/17/26</t>
+          <t>07/22/26</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Not Attempted, Permanently Closed</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>10476</t>
+          <t>10458</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>AL-3</t>
+          <t>SE-2</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D291">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Super Spirits Wine &amp; Tobacco</t>
+          <t>Southern Spirits Liquor Store</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>197 Combs Rd, Hazard, KY 41701</t>
+          <t>2815 N Main St, Hazard, Kentucky, 41701</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>08/21/26</t>
+          <t>07/17/26</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Not Attempted, Permanently Closed</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>10476</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>CB-6</t>
+          <t>AL-3</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D292">
@@ -23004,17 +23070,17 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>ARCO</t>
+          <t>Super Spirits Wine &amp; Tobacco</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>1805 Main St W, Ashland, KY 41102</t>
+          <t>197 Combs Rd, Hazard, KY 41701</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>08/17/26</t>
+          <t>08/21/26</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -23026,30 +23092,30 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>10486</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>JS-3</t>
+          <t>CB-6</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D293">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Carter Avenue Beverage Center</t>
+          <t>ARCO</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>2441 Carter Ave, Ashland, Kentucky, 41101</t>
+          <t>1805 Main St W, Ashland, KY 41102</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -23066,35 +23132,35 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>10532</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>NB-4</t>
+          <t>JS-3</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D294">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Grayson Tobacco &amp; Vape</t>
+          <t>Carter Avenue Beverage Center</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>501 N Carol Malone Blvd, Grayson, Kentucky, 41143</t>
+          <t>2441 Carter Ave, Ashland, Kentucky, 41101</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>07/29/26</t>
+          <t>08/17/26</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -23106,115 +23172,115 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>10535</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>AL-6</t>
+          <t>NB-4</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D295">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>KC's Puff &amp; Snuff</t>
+          <t>Grayson Tobacco &amp; Vape</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>21226 Highway 421, Hyden, Kentucky, 41749</t>
+          <t>501 N Carol Malone Blvd, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>07/29/26</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Ineligible - Drive Through / Gas Kiosk</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>10561</t>
+          <t>10535</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>SE-7</t>
+          <t>AL-6</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D296">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Fourseam Liquor</t>
+          <t>KC's Puff &amp; Snuff</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>3221 S Ky Highway 15, Hazard, Kentucky, 41701</t>
+          <t>21226 Highway 421, Hyden, Kentucky, 41749</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>09/17/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Ineligible - Drive Through / Gas Kiosk</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>10587</t>
+          <t>10561</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>JS-4</t>
+          <t>SE-7</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D297">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>AM PM Spirits Wine &amp; Tobacco</t>
+          <t>Fourseam Liquor</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>901 13th St, Ashland, Kentucky, 41101</t>
+          <t>3221 S Ky Highway 15, Hazard, Kentucky, 41701</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>08/18/26</t>
+          <t>09/17/26</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -23226,35 +23292,35 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>10587</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>AL-5</t>
+          <t>JS-4</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D298">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>ARCO</t>
+          <t>AM PM Spirits Wine &amp; Tobacco</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>3145 KY-15, Hazard, KY 41701</t>
+          <t>901 13th St, Ashland, Kentucky, 41101</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>09/02/26</t>
+          <t>08/18/26</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -23266,115 +23332,115 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>JS-3</t>
+          <t>AL-5</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D299">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>AAA Liquor</t>
+          <t>ARCO</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>3000 Winchester Ave., Ashland, KY 41101</t>
+          <t>3145 KY-15, Hazard, KY 41701</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>07/13/26</t>
+          <t>09/02/26</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Not Attempted, Permanently Closed</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>10596</t>
+          <t>10595</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>CB-6</t>
+          <t>JS-3</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D300">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Kroger</t>
+          <t>AAA Liquor</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>370 Diedrich Blvd, Ashland KY 41101</t>
+          <t>3000 Winchester Ave., Ashland, KY 41101</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>08/12/26</t>
+          <t>07/13/26</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Not Attempted, Permanently Closed</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>10599</t>
+          <t>10596</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>JS-6</t>
+          <t>CB-6</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D301">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>AM PM Spirits Wine &amp; Tobacco</t>
+          <t>Kroger</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>9411 US 60 Ashland, KY 41102</t>
+          <t>370 Diedrich Blvd, Ashland KY 41101</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>08/24/26</t>
+          <t>08/12/26</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -23386,12 +23452,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>10599</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>JS-2</t>
+          <t>JS-6</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -23400,7 +23466,7 @@
         </is>
       </c>
       <c r="D302">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -23409,12 +23475,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>3500 Court Street, Catlettsburg, KY 41129</t>
+          <t>9411 US 60 Ashland, KY 41102</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>08/24/26</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -23426,12 +23492,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>10601</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>JS-3</t>
+          <t>JS-2</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -23440,21 +23506,21 @@
         </is>
       </c>
       <c r="D303">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Ashland Adult Beverage Center</t>
+          <t>AM PM Spirits Wine &amp; Tobacco</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>948 29th Street Ashland, KY 41101</t>
+          <t>3500 Court Street, Catlettsburg, KY 41129</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>08/29/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -23466,12 +23532,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>JS-5</t>
+          <t>JS-3</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -23480,38 +23546,38 @@
         </is>
       </c>
       <c r="D304">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Boyd Beverage Center</t>
+          <t>Ashland Adult Beverage Center</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>1530 Shopes Creek Road, Ashland, KY 41102</t>
+          <t>948 29th Street Ashland, KY 41101</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>07/13/26</t>
+          <t>08/29/26</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Not Attempted, Permanently Closed</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>JS-1</t>
+          <t>JS-5</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -23520,141 +23586,141 @@
         </is>
       </c>
       <c r="D305">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>1st Stop Liquor</t>
+          <t>Boyd Beverage Center</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>1125 Winchester Avenue, Ashland, KY 41101</t>
+          <t>1530 Shopes Creek Road, Ashland, KY 41102</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>08/17/26</t>
+          <t>07/13/26</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Not Attempted, Permanently Closed</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>10604</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>CB-7</t>
+          <t>JS-1</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D306">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Ashland Beverage Centre</t>
+          <t>1st Stop Liquor</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>1609 Diedrich Blvd, Russell KY 41169</t>
+          <t>1125 Winchester Avenue, Ashland, KY 41101</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>08/17/26</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>JS-6</t>
+          <t>CB-7</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D307">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Good Spirits</t>
+          <t>Ashland Beverage Centre</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>1350 Wolohan Dr, Ashland, KY 41102</t>
+          <t>1609 Diedrich Blvd, Russell KY 41169</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>08/24/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>10608</t>
+          <t>10605</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>AL-4</t>
+          <t>JS-6</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D308">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Sunoco</t>
+          <t>Good Spirits</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>1366 Combs Rd, Hazard, Kentucky, 41701</t>
+          <t>1350 Wolohan Dr, Ashland, KY 41102</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>08/21/26</t>
+          <t>08/24/26</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -23666,35 +23732,35 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>10608</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>SE-5</t>
+          <t>AL-4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D309">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Whitesburg Tobacco Shed</t>
+          <t>Sunoco</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>136 Parkway Plaza Loop, Whitesburg, Kentucky, 41858</t>
+          <t>1366 Combs Rd, Hazard, Kentucky, 41701</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>08/14/26</t>
+          <t>08/21/26</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -23706,35 +23772,35 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>10610</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>NB-3</t>
+          <t>SE-5</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D310">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Dionysus Beverage Sales</t>
+          <t>Whitesburg Tobacco Shed</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>221 National Ave, Grayson, Kentucky, 41143</t>
+          <t>136 Parkway Plaza Loop, Whitesburg, Kentucky, 41858</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>07/23/26</t>
+          <t>08/14/26</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -23746,35 +23812,35 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>10611</t>
+          <t>10610</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>CB-1</t>
+          <t>NB-3</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D311">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>AM PM Liquor &amp; Tobacco</t>
+          <t>Dionysus Beverage Sales</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>46 Depot Dr, South Shore, Kentucky, 41175</t>
+          <t>221 National Ave, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>07/28/26</t>
+          <t>07/23/26</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -23786,12 +23852,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>10611</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>CB-3</t>
+          <t>CB-1</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -23800,21 +23866,21 @@
         </is>
       </c>
       <c r="D312">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Greenup Mart</t>
+          <t>AM PM Liquor &amp; Tobacco</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>1522 Seaton Ave, Greenup, Kentucky, 41144</t>
+          <t>46 Depot Dr, South Shore, Kentucky, 41175</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>08/24/26</t>
+          <t>07/28/26</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -23826,35 +23892,35 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>JS-4</t>
+          <t>CB-3</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D313">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Good Spirits</t>
+          <t>Greenup Mart</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>1117 13th St, Ashland, Kentucky, 41101</t>
+          <t>1522 Seaton Ave, Greenup, Kentucky, 41144</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>08/18/26</t>
+          <t>08/24/26</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -23866,21 +23932,21 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>10615</t>
+          <t>10614</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>CB-3</t>
+          <t>JS-4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D314">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -23889,12 +23955,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>102 Lil Way, Greenup, Kentucky, 41144</t>
+          <t>1117 13th St, Ashland, Kentucky, 41101</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>08/19/26</t>
+          <t>08/18/26</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -23906,7 +23972,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>10616</t>
+          <t>10615</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -23920,7 +23986,7 @@
         </is>
       </c>
       <c r="D315">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -23929,7 +23995,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>950 Townhill Plz, Greenup, Kentucky, 41144</t>
+          <t>102 Lil Way, Greenup, Kentucky, 41144</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -23939,82 +24005,82 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Not Attempted, Permanently Closed</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>10616</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>JS-7</t>
+          <t>CB-3</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D316">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Mud Slingers</t>
+          <t>Good Spirits</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>14778 State Route 854, Rush, Kentucky, 41168</t>
+          <t>950 Townhill Plz, Greenup, Kentucky, 41144</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>07/30/26</t>
+          <t>08/19/26</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Not Attempted, Permanently Closed</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>10632</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>SE-3</t>
+          <t>JS-7</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D317">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Fast Track #5</t>
+          <t>Mud Slingers</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>3668 Highway 582, Pine Top, Kentucky, 41843</t>
+          <t>14778 State Route 854, Rush, Kentucky, 41168</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>09/01/26</t>
+          <t>07/30/26</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -24026,12 +24092,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>SE-4</t>
+          <t>SE-3</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -24040,38 +24106,38 @@
         </is>
       </c>
       <c r="D318">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Wildcats Country Market</t>
+          <t>Fast Track #5</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>8649 KY Highway 7, Viper, Kentucky, 41774</t>
+          <t>3668 Highway 582, Pine Top, Kentucky, 41843</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>07/29/26</t>
+          <t>09/01/26</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Not Attempted, Permanently Closed</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>10639</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>SE-7</t>
+          <t>SE-4</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -24080,117 +24146,117 @@
         </is>
       </c>
       <c r="D319">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Wildcats Country Market</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>317 Happy Cir, Happy, Kentucky, 41746</t>
+          <t>8649 KY Highway 7, Viper, Kentucky, 41774</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>07/16/26</t>
+          <t>07/29/26</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Not Attempted, Permanently Closed</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>10642</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>AL-1</t>
+          <t>SE-7</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D320">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>DG Market</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>59 Highway 15 N, Jackson, Kentucky, 41339</t>
+          <t>317 Happy Cir, Happy, Kentucky, 41746</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>07/16/26</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>10643</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>CB-6</t>
+          <t>AL-1</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D321">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>DG Market</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>259 Wheatley Rd, Ashland, Kentucky, 41101</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>08/17/26</t>
-        </is>
-      </c>
-      <c r="H321" t="inlineStr">
-        <is>
-          <t>Eligible, Audit Completed</t>
+          <t>59 Highway 15 N, Jackson, Kentucky, 41339</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>10646</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>NB-6</t>
+          <t>CB-6</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D322">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
@@ -24199,12 +24265,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>10349 Highway 15 S, Lost Creek, Kentucky, 41348</t>
+          <t>259 Wheatley Rd, Ashland, Kentucky, 41101</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>07/21/26</t>
+          <t>08/17/26</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -24216,12 +24282,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>10647</t>
+          <t>10646</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>NB-5</t>
+          <t>NB-6</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -24230,21 +24296,21 @@
         </is>
       </c>
       <c r="D323">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Grayson Beverage Center</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>126 Interstate Dr, Grayson, Kentucky, 41143</t>
+          <t>10349 Highway 15 S, Lost Creek, Kentucky, 41348</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>08/21/26</t>
+          <t>07/21/26</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -24256,12 +24322,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>10647</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>NB-4</t>
+          <t>NB-5</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -24270,16 +24336,16 @@
         </is>
       </c>
       <c r="D324">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Smoker Friendly</t>
+          <t>Grayson Beverage Center</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>517 E Main St, Grayson, Kentucky, 41143</t>
+          <t>126 Interstate Dr, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -24336,122 +24402,122 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>10649</t>
+          <t>10648</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>CB-4</t>
+          <t>NB-4</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D326">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Sams Carryout</t>
+          <t>Smoker Friendly</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>715 Greenup Ave, Russell, Kentucky, 41169</t>
+          <t>517 E Main St, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>08/21/26</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>SE-1</t>
+          <t>CB-4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D327">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Fast Track</t>
+          <t>Sams Carryout</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>104 Highway 899, Hindman, Kentucky, 41822</t>
+          <t>715 Greenup Ave, Russell, Kentucky, 41169</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>10651</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>AL-6</t>
+          <t>SE-1</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D328">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Mountain Liquor</t>
+          <t>Fast Track</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>21400 US-421, Hyden, KY 41749</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>08/26/26</t>
-        </is>
-      </c>
-      <c r="H328" t="inlineStr">
-        <is>
-          <t>Eligible, Audit Completed</t>
+          <t>104 Highway 899, Hindman, Kentucky, 41822</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>10653</t>
+          <t>10651</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>AL-3</t>
+          <t>AL-6</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -24460,21 +24526,21 @@
         </is>
       </c>
       <c r="D329">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Brewers Liquors</t>
+          <t>Mountain Liquor</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>611 Memorial Dr, Hazard, Kentucky, 41701</t>
+          <t>21400 US-421, Hyden, KY 41749</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>07/29/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -24486,12 +24552,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>10655</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>AL-5</t>
+          <t>AL-3</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -24500,21 +24566,21 @@
         </is>
       </c>
       <c r="D330">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>56 Wine &amp; Spirits</t>
+          <t>Brewers Liquors</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>3256 W KY Highway 80, Hazard, Kentucky, 41701</t>
+          <t>611 Memorial Dr, Hazard, Kentucky, 41701</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>09/01/26</t>
+          <t>07/29/26</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -24526,35 +24592,35 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10655</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>SE-2</t>
+          <t>AL-5</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D331">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Go Time</t>
+          <t>56 Wine &amp; Spirits</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>32 Constitution Ave, Hazard, KY 41701</t>
+          <t>3256 W KY Highway 80, Hazard, Kentucky, 41701</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>09/01/26</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -24566,35 +24632,35 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>10656</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>AL-4</t>
+          <t>SE-2</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D332">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Top of the Hill Liquors LLC</t>
+          <t>Go Time</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>33 Boone Ridge Rd, Hazard, Kentucky, 41701</t>
+          <t>32 Constitution Ave, Hazard, KY 41701</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>09/24/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -24606,35 +24672,35 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>10658</t>
+          <t>10657</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>CB-4</t>
+          <t>AL-4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D333">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>DG Market</t>
+          <t>Top of the Hill Liquors LLC</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>652 Heaberlin Rd, Greenup, Kentucky, 41144</t>
+          <t>33 Boone Ridge Rd, Hazard, Kentucky, 41701</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>07/23/26</t>
+          <t>09/24/26</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -24646,12 +24712,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>CB-7</t>
+          <t>CB-4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -24660,21 +24726,21 @@
         </is>
       </c>
       <c r="D334">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>DG Market</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>4501 State Route 2, Greenup, Kentucky, 41144</t>
+          <t>652 Heaberlin Rd, Greenup, Kentucky, 41144</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>07/20/26</t>
+          <t>07/23/26</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -24686,35 +24752,35 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>SE-4</t>
+          <t>CB-7</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D335">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Soggy Bottom General Store</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>83 Left Fork Maces Creek Rd, Viper, Kentucky, 41774</t>
+          <t>4501 State Route 2, Greenup, Kentucky, 41144</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>07/29/26</t>
+          <t>07/20/26</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -24726,7 +24792,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>10661</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -24740,16 +24806,16 @@
         </is>
       </c>
       <c r="D336">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>The Front Porch 2</t>
+          <t>Soggy Bottom General Store</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>35 KY Highway 463, Slemp, Kentucky, 41763</t>
+          <t>83 Left Fork Maces Creek Rd, Viper, Kentucky, 41774</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -24766,12 +24832,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>10661</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>SE-2</t>
+          <t>SE-4</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -24780,28 +24846,38 @@
         </is>
       </c>
       <c r="D337">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>The Moon Spirits</t>
+          <t>The Front Porch 2</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>388 Highway 80 E, Hindman, Kentucky, 41822</t>
+          <t>35 KY Highway 463, Slemp, Kentucky, 41763</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>07/29/26</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10662</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>SE-4</t>
+          <t>SE-2</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -24810,61 +24886,51 @@
         </is>
       </c>
       <c r="D338">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Viper Hardware</t>
+          <t>The Moon Spirits</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>8728 KY Highway 7, Viper, Kentucky, 41774</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>09/17/26</t>
-        </is>
-      </c>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>Eligible, Audit Completed</t>
+          <t>388 Highway 80 E, Hindman, Kentucky, 41822</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>NB-1</t>
+          <t>SE-4</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D339">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>AM PM Spirits Wine &amp; Tobacco</t>
+          <t>Viper Hardware</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>131 Jessica Ln, Suite E, Olive Hill, KY 41164</t>
+          <t>8728 KY Highway 7, Viper, Kentucky, 41774</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>07/30/26</t>
+          <t>09/17/26</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -24876,12 +24942,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>10665</t>
+          <t>10664</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>NB-3</t>
+          <t>NB-1</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -24890,21 +24956,21 @@
         </is>
       </c>
       <c r="D340">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>T &amp; T Outdoors</t>
+          <t>AM PM Spirits Wine &amp; Tobacco</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>4609 S State Highway 7, Grayson, Kentucky, 41143</t>
+          <t>131 Jessica Ln, Suite E, Olive Hill, KY 41164</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>07/23/26</t>
+          <t>07/30/26</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -24916,35 +24982,35 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>10666</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>CB-1</t>
+          <t>NB-3</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D341">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Jenny's Mart</t>
+          <t>T &amp; T Outdoors</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>1337 KY-8, South Portsmouth, KY 41174</t>
+          <t>4609 S State Highway 7, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>07/28/26</t>
+          <t>07/23/26</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -24956,132 +25022,132 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>10667</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>JS-2</t>
+          <t>CB-1</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D342">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Cigarette Outlet</t>
+          <t>Jenny's Mart</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>308 35th St, Catlettsburg, Kentucky, 41129</t>
+          <t>1337 KY-8, South Portsmouth, KY 41174</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>08/27/26</t>
+          <t>07/28/26</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>10668</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>CB-5</t>
+          <t>JS-2</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D343">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goodfell's Tobacco Store </t>
+          <t>Cigarette Outlet</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>2002 Argillite Rd, Flatwoods, Kentucky, 41139</t>
+          <t>308 35th St, Catlettsburg, Kentucky, 41129</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>07/23/26</t>
+          <t>08/27/26</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Not Attempted, Permanently Closed</t>
+          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>10669</t>
+          <t>10668</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>JS-5</t>
+          <t>CB-5</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D344">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Fat Ash Cigar Lounge</t>
+          <t xml:space="preserve">Goodfell's Tobacco Store </t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>8110 US Route 60, Ashland, Kentucky, 41102</t>
+          <t>2002 Argillite Rd, Flatwoods, Kentucky, 41139</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>07/13/26</t>
+          <t>07/23/26</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Not Attempted, Permanently Closed</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10669</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>JS-1</t>
+          <t>JS-5</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -25090,16 +25156,16 @@
         </is>
       </c>
       <c r="D345">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Phoenix Vapors</t>
+          <t>Fat Ash Cigar Lounge</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>222 16th St, Ashland, Kentucky, 41101</t>
+          <t>8110 US Route 60, Ashland, Kentucky, 41102</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -25109,62 +25175,102 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>10670</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>NB-4</t>
+          <t>JS-1</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D346">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Tobacco Barn</t>
+          <t>Phoenix Vapors</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>521 E Main St, Grayson, Kentucky, 41143</t>
+          <t>222 16th St, Ashland, Kentucky, 41101</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>08/21/26</t>
+          <t>07/13/26</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Not Attempted, Permanently Closed</t>
+          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
+          <t>10671</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>NB-4</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D347">
+        <v>3</v>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Tobacco Barn</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>521 E Main St, Grayson, Kentucky, 41143</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>08/21/26</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Not Attempted, Permanently Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
           <t>T_Store999</t>
         </is>
       </c>
-      <c r="G347" t="inlineStr">
+      <c r="G348" t="inlineStr">
         <is>
           <t>07/22/26</t>
         </is>
       </c>
-      <c r="H347" t="inlineStr">
+      <c r="H348" t="inlineStr">
         <is>
           <t>Ineligible - Drive Through / Gas Kiosk</t>
         </is>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1549,26 +1549,76 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>10/04/26</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>10/07/26</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>2</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B48">
+      <c r="B50">
         <v>32</v>
       </c>
-      <c r="C48">
+      <c r="C50">
         <v>73</v>
       </c>
-      <c r="D48">
-        <v>55</v>
-      </c>
-      <c r="E48">
+      <c r="D50">
+        <v>56</v>
+      </c>
+      <c r="E50">
         <v>84</v>
       </c>
-      <c r="F48">
-        <v>50</v>
-      </c>
-      <c r="G48">
-        <v>294</v>
+      <c r="F50">
+        <v>52</v>
+      </c>
+      <c r="G50">
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -1578,7 +1628,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AX14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1829,6 +1879,16 @@
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
+          <t>10/04/26</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>10/07/26</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1984,7 +2044,13 @@
         <v>3</v>
       </c>
       <c r="AX2">
-        <v>294</v>
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>2</v>
+      </c>
+      <c r="AZ2">
+        <v>297</v>
       </c>
     </row>
     <row r="3">
@@ -2138,6 +2204,12 @@
         <v>2</v>
       </c>
       <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
         <v>6</v>
       </c>
     </row>
@@ -2292,6 +2364,12 @@
         <v>0</v>
       </c>
       <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
         <v>1</v>
       </c>
     </row>
@@ -2448,6 +2526,12 @@
       <c r="AX5">
         <v>0</v>
       </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2602,6 +2686,12 @@
       <c r="AX6">
         <v>0</v>
       </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2754,6 +2844,12 @@
         <v>0</v>
       </c>
       <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
         <v>18</v>
       </c>
     </row>
@@ -2908,6 +3004,12 @@
         <v>0</v>
       </c>
       <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
         <v>1</v>
       </c>
     </row>
@@ -3062,6 +3164,12 @@
         <v>0</v>
       </c>
       <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
         <v>2</v>
       </c>
     </row>
@@ -3218,6 +3326,12 @@
       <c r="AX10">
         <v>0</v>
       </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3370,6 +3484,12 @@
         <v>0</v>
       </c>
       <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
         <v>8</v>
       </c>
     </row>
@@ -3524,6 +3644,12 @@
         <v>0</v>
       </c>
       <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
         <v>3</v>
       </c>
     </row>
@@ -3678,6 +3804,12 @@
         <v>0</v>
       </c>
       <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
         <v>4</v>
       </c>
     </row>
@@ -3832,7 +3964,13 @@
         <v>5</v>
       </c>
       <c r="AX14">
-        <v>337</v>
+        <v>1</v>
+      </c>
+      <c r="AY14">
+        <v>2</v>
+      </c>
+      <c r="AZ14">
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -3895,16 +4033,16 @@
         <v>73</v>
       </c>
       <c r="D2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E2">
         <v>84</v>
       </c>
       <c r="F2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G2">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3">
@@ -4195,16 +4333,16 @@
         <v>84</v>
       </c>
       <c r="D14">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E14">
         <v>92</v>
       </c>
       <c r="F14">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G14">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -4214,7 +4352,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D346"/>
+  <dimension ref="A1:D349"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -11784,6 +11922,72 @@
         </is>
       </c>
       <c r="D346" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>New_Store999</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>10/04/26</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>10263</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>10/07/26</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>10/07/26</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
         <is>
           <t>Eligible, Audit Completed</t>
         </is>
@@ -11796,7 +12000,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H350"/>
+  <dimension ref="A1:H351"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -11872,12 +12076,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>09/01/26</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Eligible, Asked to Leave Before Audit Started - Permission Not Given</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
@@ -11912,12 +12116,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>09/01/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Eligible, Asked to Leave Before Audit Started - Permission Not Given</t>
         </is>
       </c>
     </row>
@@ -11952,7 +12156,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>08/20/26</t>
+          <t>08/12/26</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -11992,7 +12196,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>08/12/26</t>
+          <t>08/20/26</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -13227,7 +13431,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>07/23/26</t>
+          <t>09/22/26</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
@@ -13262,12 +13471,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>09/22/26</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Eligible, Audit Completed</t>
+          <t>07/23/26</t>
         </is>
       </c>
     </row>
@@ -16052,12 +16256,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>07/22/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Other Disposition (Please Describe)</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
@@ -16092,12 +16296,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>07/22/26</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Other Disposition (Please Describe)</t>
         </is>
       </c>
     </row>
@@ -17175,6 +17379,11 @@
           <t>08/26/26</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -17210,11 +17419,6 @@
           <t>08/26/26</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Eligible, Audit Completed</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -21225,6 +21429,16 @@
           <t>32 Lost Creek Rd Dice, Hazard, KY 41722</t>
         </is>
       </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>10/07/26</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -21297,7 +21511,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>08/31/26</t>
+          <t>08/27/26</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -21337,7 +21551,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>08/27/26</t>
+          <t>08/31/26</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -21780,6 +21994,11 @@
           <t>07/20/26</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -21815,11 +22034,6 @@
           <t>07/20/26</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Eligible, Audit Completed</t>
-        </is>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -22292,12 +22506,12 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>07/22/26</t>
+          <t>09/30/26</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Re-Attempt Needed, Temporarily Closed</t>
+          <t>Eligible, Asked to Leave Before Audit Started - Permission Not Given</t>
         </is>
       </c>
     </row>
@@ -22332,12 +22546,12 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>09/30/26</t>
+          <t>07/22/26</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Eligible, Asked to Leave Before Audit Started - Permission Not Given</t>
+          <t>Re-Attempt Needed, Temporarily Closed</t>
         </is>
       </c>
     </row>
@@ -22530,6 +22744,16 @@
           <t>112 KY-899, Hindman, Kentucky, 41822</t>
         </is>
       </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>10/07/26</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -22722,7 +22946,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>08/31/26</t>
+          <t>07/28/26</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -22762,7 +22986,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>07/28/26</t>
+          <t>08/31/26</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -25684,15 +25908,32 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
+          <t>New_Store999</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>10/04/26</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
           <t>T_Store999</t>
         </is>
       </c>
-      <c r="G350" t="inlineStr">
+      <c r="G351" t="inlineStr">
         <is>
           <t>07/22/26</t>
         </is>
       </c>
-      <c r="H350" t="inlineStr">
+      <c r="H351" t="inlineStr">
         <is>
           <t>Ineligible - Drive Through / Gas Kiosk</t>
         </is>
@@ -25705,7 +25946,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -26013,12 +26254,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SE-1</t>
+          <t>SE-4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -26027,74 +26268,14 @@
         </is>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hindman Quick Stop # 7</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
-        <is>
-          <t>112 KY-899, Hindman, Kentucky, 41822</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10263</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SE-2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>BP</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>32 Lost Creek Rd Dice, Hazard, KY 41722</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>10208</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SE-4</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Shell</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
         <is>
           <t>108 E Main St, Hazard, Kentucky, 41701</t>
         </is>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1574,11 +1574,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10/07/26</t>
+          <t>10/06/26</t>
         </is>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -1590,35 +1590,85 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>10/07/26</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>2</v>
+      </c>
+      <c r="G50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>10/08/26</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B50">
-        <v>32</v>
-      </c>
-      <c r="C50">
+      <c r="B52">
+        <v>33</v>
+      </c>
+      <c r="C52">
         <v>73</v>
       </c>
-      <c r="D50">
+      <c r="D52">
         <v>56</v>
       </c>
-      <c r="E50">
+      <c r="E52">
         <v>84</v>
       </c>
-      <c r="F50">
-        <v>52</v>
-      </c>
-      <c r="G50">
-        <v>297</v>
+      <c r="F52">
+        <v>53</v>
+      </c>
+      <c r="G52">
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -1628,7 +1678,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:BB14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1884,10 +1934,20 @@
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
+          <t>10/06/26</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
           <t>10/07/26</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>10/08/26</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -2047,10 +2107,16 @@
         <v>1</v>
       </c>
       <c r="AY2">
+        <v>1</v>
+      </c>
+      <c r="AZ2">
         <v>2</v>
       </c>
-      <c r="AZ2">
-        <v>297</v>
+      <c r="BA2">
+        <v>1</v>
+      </c>
+      <c r="BB2">
+        <v>299</v>
       </c>
     </row>
     <row r="3">
@@ -2210,6 +2276,12 @@
         <v>0</v>
       </c>
       <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
+      <c r="BB3">
         <v>6</v>
       </c>
     </row>
@@ -2370,6 +2442,12 @@
         <v>0</v>
       </c>
       <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
         <v>1</v>
       </c>
     </row>
@@ -2532,6 +2610,12 @@
       <c r="AZ5">
         <v>0</v>
       </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2692,6 +2776,12 @@
       <c r="AZ6">
         <v>0</v>
       </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2850,6 +2940,12 @@
         <v>0</v>
       </c>
       <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
         <v>18</v>
       </c>
     </row>
@@ -3010,6 +3106,12 @@
         <v>0</v>
       </c>
       <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
         <v>1</v>
       </c>
     </row>
@@ -3170,6 +3272,12 @@
         <v>0</v>
       </c>
       <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
         <v>2</v>
       </c>
     </row>
@@ -3332,6 +3440,12 @@
       <c r="AZ10">
         <v>0</v>
       </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3490,6 +3604,12 @@
         <v>0</v>
       </c>
       <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
         <v>8</v>
       </c>
     </row>
@@ -3650,6 +3770,12 @@
         <v>0</v>
       </c>
       <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
         <v>3</v>
       </c>
     </row>
@@ -3807,10 +3933,16 @@
         <v>0</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ13">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -3970,7 +4102,13 @@
         <v>2</v>
       </c>
       <c r="AZ14">
-        <v>340</v>
+        <v>2</v>
+      </c>
+      <c r="BA14">
+        <v>1</v>
+      </c>
+      <c r="BB14">
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -4027,7 +4165,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2">
         <v>73</v>
@@ -4039,10 +4177,10 @@
         <v>84</v>
       </c>
       <c r="F2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G2">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3">
@@ -4302,7 +4440,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -4317,7 +4455,7 @@
         <v>2</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -4327,7 +4465,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>84</v>
@@ -4339,10 +4477,10 @@
         <v>92</v>
       </c>
       <c r="F14">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G14">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -4352,7 +4490,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D349"/>
+  <dimension ref="A1:D352"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -11988,6 +12126,72 @@
         </is>
       </c>
       <c r="D349" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>10256</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>10/06/26</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Other Disposition (Please Describe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>10642</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>10/06/26</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>10/08/26</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
         <is>
           <t>Eligible, Audit Completed</t>
         </is>
@@ -12000,7 +12204,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H351"/>
+  <dimension ref="A1:H352"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -19564,6 +19768,16 @@
           <t>108 E Main St, Hazard, Kentucky, 41701</t>
         </is>
       </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>10/08/26</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -21243,75 +21457,75 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>10258</t>
+          <t>10256</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>JS-3</t>
+          <t>AL-1</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D233">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Exxon</t>
+          <t>Ancient Wisdom</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>3500 Winchester Ave, Ashland, Kentucky, 41101</t>
+          <t>357 KY-15, Jackson, Kentucky, 41339</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>08/10/26</t>
+          <t>10/06/26</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Other Disposition (Please Describe)</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>10259</t>
+          <t>10258</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>SE-6</t>
+          <t>JS-3</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D234">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Price Less Foods</t>
+          <t>Exxon</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>34 Whitesburg Plz, Whitesburg, Kentucky, 41858</t>
+          <t>3500 Winchester Ave, Ashland, Kentucky, 41101</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>09/18/26</t>
+          <t>08/10/26</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -21323,35 +21537,35 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>10259</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>AL-7</t>
+          <t>SE-6</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D235">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>T-Mart</t>
+          <t>Price Less Foods</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>33155 US-421, Bear Branch, Kentucky, 41714</t>
+          <t>34 Whitesburg Plz, Whitesburg, Kentucky, 41858</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>08/12/26</t>
+          <t>09/18/26</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -21363,35 +21577,35 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>CB-2</t>
+          <t>AL-7</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D236">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Cigs for Less</t>
+          <t>T-Mart</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>32 Pierce St, Greenup, Kentucky, 41144</t>
+          <t>33155 US-421, Bear Branch, Kentucky, 41714</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>08/24/26</t>
+          <t>08/12/26</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -21403,17 +21617,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>10263</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>SE-2</t>
+          <t>CB-2</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D237">
@@ -21421,17 +21635,17 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>Cigs for Less</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>32 Lost Creek Rd Dice, Hazard, KY 41722</t>
+          <t>32 Pierce St, Greenup, Kentucky, 41144</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>10/07/26</t>
+          <t>08/24/26</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -21443,35 +21657,35 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>10265</t>
+          <t>10263</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>JS-3</t>
+          <t>SE-2</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D238">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Fatcat Smokes</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>3098 Winchester Ave, Ashland, Kentucky, 41101</t>
+          <t>32 Lost Creek Rd Dice, Hazard, KY 41722</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>07/27/26</t>
+          <t>10/07/26</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -21483,12 +21697,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>10267</t>
+          <t>10265</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>JS-2</t>
+          <t>JS-3</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -21497,21 +21711,21 @@
         </is>
       </c>
       <c r="D239">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>First &amp; Last Tobacco LLC</t>
+          <t>Fatcat Smokes</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>300 35th St, Catlettsburg, Kentucky, 41129</t>
+          <t>3098 Winchester Ave, Ashland, Kentucky, 41101</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>08/27/26</t>
+          <t>07/27/26</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -21551,7 +21765,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>08/31/26</t>
+          <t>08/27/26</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -21563,35 +21777,35 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>10267</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>SE-5</t>
+          <t>JS-2</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D241">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Isom IGA</t>
+          <t>First &amp; Last Tobacco LLC</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>29 Isom Dr, Isom, Kentucky, 41824</t>
+          <t>300 35th St, Catlettsburg, Kentucky, 41129</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>08/14/26</t>
+          <t>08/31/26</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -21603,35 +21817,35 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>10268</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>CB-2</t>
+          <t>SE-5</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D242">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Clark's Pump-N-Shop</t>
+          <t>Isom IGA</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>28248 US-23, South Shore, KY 41175</t>
+          <t>29 Isom Dr, Isom, Kentucky, 41824</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>08/24/26</t>
+          <t>08/14/26</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -21643,35 +21857,35 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>10270</t>
+          <t>10269</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>SE-2</t>
+          <t>CB-2</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D243">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Double Kwik</t>
+          <t>Clark's Pump-N-Shop</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>28 KY-80, Hindman, Kentucky, 41822</t>
+          <t>28248 US-23, South Shore, KY 41175</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>10/01/26</t>
+          <t>08/24/26</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -21683,35 +21897,35 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>10271</t>
+          <t>10270</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>NB-1</t>
+          <t>SE-2</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D244">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>Double Kwik</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>2464 State Highway 2, Olive Hill, Kentucky, 41164</t>
+          <t>28 KY-80, Hindman, Kentucky, 41822</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>07/30/26</t>
+          <t>10/01/26</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -21723,35 +21937,35 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>10271</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>CB-2</t>
+          <t>NB-1</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D245">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Webbs Country Market</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>24165 State Route 7, Greenup, Kentucky, 41144</t>
+          <t>2464 State Highway 2, Olive Hill, Kentucky, 41164</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>07/20/26</t>
+          <t>07/30/26</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -21763,12 +21977,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>10273</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>CB-5</t>
+          <t>CB-2</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -21777,21 +21991,21 @@
         </is>
       </c>
       <c r="D246">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Smoker Friendly</t>
+          <t>Webbs Country Market</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>2307 Argillite Rd, Flatwoods, Kentucky, 41139</t>
+          <t>24165 State Route 7, Greenup, Kentucky, 41144</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>08/07/26</t>
+          <t>07/20/26</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -21803,35 +22017,35 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>10274</t>
+          <t>10273</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>AL-6</t>
+          <t>CB-5</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D247">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Hyden Double Kwik</t>
+          <t>Smoker Friendly</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>22380 Main St, Hyden, Kentucky, 41749</t>
+          <t>2307 Argillite Rd, Flatwoods, Kentucky, 41139</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>08/07/26</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -21843,35 +22057,35 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>10274</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>JS-1</t>
+          <t>AL-6</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D248">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Sunoco</t>
+          <t>Hyden Double Kwik</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>2201 Winchester Ave, Ashland, KY 41101</t>
+          <t>22380 Main St, Hyden, Kentucky, 41749</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>08/31/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -21883,35 +22097,35 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>10276</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>AL-1</t>
+          <t>JS-1</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D249">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>VIP Fuels</t>
+          <t>Sunoco</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>30 KY-15, Jackson, KY 41339</t>
+          <t>2201 Winchester Ave, Ashland, KY 41101</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>09/04/26</t>
+          <t>08/31/26</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -21923,12 +22137,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>10276</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>AL-6</t>
+          <t>AL-1</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -21937,66 +22151,66 @@
         </is>
       </c>
       <c r="D250">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Cox Iga Supermarkets</t>
+          <t>VIP Fuels</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>21224 US-421, Hyden, KY 41749</t>
+          <t>30 KY-15, Jackson, KY 41339</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>09/04/26</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>10279</t>
+          <t>10278</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>JS-6</t>
+          <t>AL-6</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D251">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Marathon</t>
+          <t>Cox Iga Supermarkets</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>2100 State Route 3, Catlettsburg, Kentucky, 41129</t>
+          <t>21224 US-421, Hyden, KY 41749</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>07/20/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
         </is>
       </c>
     </row>
@@ -22034,25 +22248,30 @@
           <t>07/20/26</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>10280</t>
+          <t>10279</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>AL-1</t>
+          <t>JS-6</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D253">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -22061,17 +22280,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>20 North Point Ave, Jackson, KY 41339</t>
+          <t>2100 State Route 3, Catlettsburg, Kentucky, 41129</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>08/29/26</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>Eligible, Audit Completed</t>
+          <t>07/20/26</t>
         </is>
       </c>
     </row>
@@ -22118,17 +22332,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>10281</t>
+          <t>10280</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>JS-7</t>
+          <t>AL-1</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D255">
@@ -22136,17 +22350,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>ARCO</t>
+          <t>Marathon</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>1965 US Route 60, Rush, Kentucky, 41168</t>
+          <t>20 North Point Ave, Jackson, KY 41339</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>08/22/26</t>
+          <t>08/29/26</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -22158,35 +22372,35 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10281</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>AL-4</t>
+          <t>JS-7</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D256">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Mountain Vapors</t>
+          <t>ARCO</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>181 Village Ln, Hazard, Kentucky, 41701</t>
+          <t>1965 US Route 60, Rush, Kentucky, 41168</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>08/20/26</t>
+          <t>08/22/26</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -22198,35 +22412,35 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>10283</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>NB-3</t>
+          <t>AL-4</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D257">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Exxon</t>
+          <t>Mountain Vapors</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>178 S Carol Malone Blvd, Grayson, Kentucky, 41143</t>
+          <t>181 Village Ln, Hazard, Kentucky, 41701</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>07/29/26</t>
+          <t>08/20/26</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -22238,115 +22452,115 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>10283</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>JS-1</t>
+          <t>NB-3</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D258">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Vapor World</t>
+          <t>Exxon</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>1600 Greenup Ave, Ashland, Kentucky, 41101</t>
+          <t>178 S Carol Malone Blvd, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>07/13/26</t>
+          <t>07/29/26</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Not Attempted, Permanently Closed</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>10287</t>
+          <t>10286</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>NB-6</t>
+          <t>JS-1</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D259">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Vapor World</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>1589 Kentucky Ave, Jackson, KY 41339</t>
+          <t>1600 Greenup Ave, Ashland, Kentucky, 41101</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>07/21/26</t>
+          <t>07/13/26</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Not Attempted, Permanently Closed</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>10287</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>CB-5</t>
+          <t>NB-6</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D260">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>1510 Argillite Rd, Flatwoods, Kentucky, 41139</t>
+          <t>1589 Kentucky Ave, Jackson, KY 41339</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>08/17/26</t>
+          <t>07/21/26</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -22358,12 +22572,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>10291</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>CB-1</t>
+          <t>CB-5</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -22372,21 +22586,21 @@
         </is>
       </c>
       <c r="D261">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>SQ Liquor</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>142 James E Hannah Dr, South Shore, Kentucky, 41175</t>
+          <t>1510 Argillite Rd, Flatwoods, Kentucky, 41139</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>08/31/26</t>
+          <t>08/17/26</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -22426,7 +22640,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>07/28/26</t>
+          <t>08/31/26</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -22438,7 +22652,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>10292</t>
+          <t>10291</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -22452,16 +22666,16 @@
         </is>
       </c>
       <c r="D263">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Marathon</t>
+          <t>SQ Liquor</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>1376 State Route 8, South Portsmouth, Kentucky, 41174</t>
+          <t>142 James E Hannah Dr, South Shore, Kentucky, 41175</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -22478,40 +22692,40 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>10292</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>SE-1</t>
+          <t>CB-1</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D264">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Double J Tobacco</t>
+          <t>Marathon</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>1256 Highway 160 S, Hindman, Kentucky, 41822</t>
+          <t>1376 State Route 8, South Portsmouth, Kentucky, 41174</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>09/30/26</t>
+          <t>07/28/26</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Eligible, Asked to Leave Before Audit Started - Permission Not Given</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
@@ -22586,7 +22800,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>09/30/26</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -22598,155 +22812,155 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>10293</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>JS-6</t>
+          <t>SE-1</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D267">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Smokin Toms</t>
+          <t>Double J Tobacco</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>12484 US Route 60, Ashland, Kentucky, 41102</t>
+          <t>1256 Highway 160 S, Hindman, Kentucky, 41822</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>08/24/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Eligible, Asked to Leave Before Audit Started - Permission Not Given</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>10294</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>NB-4</t>
+          <t>JS-6</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D268">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>The Eastern Kentucky Hemp Company</t>
+          <t>Smokin Toms</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>123 E Main St, Grayson, Kentucky, 41143</t>
+          <t>12484 US Route 60, Ashland, Kentucky, 41102</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>08/21/26</t>
+          <t>08/24/26</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Not Attempted, Permanently Closed</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>CB-4</t>
+          <t>NB-4</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D269">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Marathon</t>
+          <t>The Eastern Kentucky Hemp Company</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>11825 US 23 Hwy, Greenup, Kentucky, 41144</t>
+          <t>123 E Main St, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>08/24/26</t>
+          <t>08/21/26</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Not Attempted, Permanently Closed</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>SE-1</t>
+          <t>CB-4</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D270">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Hindman Quick Stop # 7</t>
+          <t>Marathon</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>112 KY-899, Hindman, Kentucky, 41822</t>
+          <t>11825 US 23 Hwy, Greenup, Kentucky, 41144</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>10/07/26</t>
+          <t>08/24/26</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -22758,35 +22972,35 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>CB-3</t>
+          <t>SE-1</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D271">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Greenup Tobacco and Beer</t>
+          <t>Hindman Quick Stop # 7</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>1103 Seaton Ave, Greenup, Kentucky, 41144</t>
+          <t>112 KY-899, Hindman, Kentucky, 41822</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>08/19/26</t>
+          <t>10/07/26</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -22798,17 +23012,17 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>JS-6</t>
+          <t>CB-3</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D272">
@@ -22816,17 +23030,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Exxon</t>
+          <t>Greenup Tobacco and Beer</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>10973 US Route 60, Ashland, Kentucky, 41102</t>
+          <t>1103 Seaton Ave, Greenup, Kentucky, 41144</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>08/24/26</t>
+          <t>08/19/26</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -22838,35 +23052,35 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>NB-2</t>
+          <t>JS-6</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D273">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Marathon</t>
+          <t>Exxon</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>1051 N State Highway 7, Grayson, Kentucky, 41143</t>
+          <t>10973 US Route 60, Ashland, Kentucky, 41102</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>07/22/26</t>
+          <t>08/24/26</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -22878,35 +23092,35 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>SE-7</t>
+          <t>NB-2</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D274">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Happy IGA</t>
+          <t>Marathon</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>10036 KY-15, Happy, Kentucky, 41746</t>
+          <t>1051 N State Highway 7, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>09/17/26</t>
+          <t>07/22/26</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -22918,35 +23132,35 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>CB-2</t>
+          <t>SE-7</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D275">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Happy IGA</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>10003 KY-7, South Shore, Kentucky, 41175</t>
+          <t>10036 KY-15, Happy, Kentucky, 41746</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>07/28/26</t>
+          <t>09/17/26</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -22986,7 +23200,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>08/31/26</t>
+          <t>07/28/26</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -22998,115 +23212,115 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>10309</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>SE-2</t>
+          <t>CB-2</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D277">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Cardinal Country Store</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>100 Jamestown Vlg, Hazard, Kentucky, 41701</t>
+          <t>10003 KY-7, South Shore, Kentucky, 41175</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>08/31/26</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Eligible, Asked to Leave During Audit - Audit Partially Complete</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>10310</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>AL-2</t>
+          <t>SE-2</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D278">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Nabels</t>
+          <t>Cardinal Country Store</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>3108 KY-28, Hazard, Kentucky, 41701</t>
+          <t>100 Jamestown Vlg, Hazard, Kentucky, 41701</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>08/18/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Eligible, Asked to Leave During Audit - Audit Partially Complete</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10310</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>JS-1</t>
+          <t>AL-2</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D279">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Ashland Beverage Centre</t>
+          <t>Nabels</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>744 Winchester Ave, Ashland, Kentucky, 41101</t>
+          <t>3108 KY-28, Hazard, Kentucky, 41701</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>07/18/26</t>
+          <t>08/18/26</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -23118,35 +23332,35 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10314</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>AL-7</t>
+          <t>JS-1</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D280">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Rocks Market</t>
+          <t>Ashland Beverage Centre</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>1571 Highway 421, Bledsoe, Kentucky, 40810</t>
+          <t>744 Winchester Ave, Ashland, Kentucky, 41101</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>08/12/26</t>
+          <t>07/18/26</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -23158,35 +23372,35 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>10327</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>SE-2</t>
+          <t>AL-7</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D281">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>The Honey Hole on East 80</t>
+          <t>Rocks Market</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>7934 E Ky Highway 80, Hazard, Kentucky, 41701</t>
+          <t>1571 Highway 421, Bledsoe, Kentucky, 40810</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>08/12/26</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -23198,12 +23412,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>SE-3</t>
+          <t>SE-2</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -23212,21 +23426,21 @@
         </is>
       </c>
       <c r="D282">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>IGA food world</t>
+          <t>The Honey Hole on East 80</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>3149 Highway 805, Neon, Kentucky, 41840</t>
+          <t>7934 E Ky Highway 80, Hazard, Kentucky, 41701</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>09/01/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -23238,115 +23452,115 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>10349</t>
+          <t>10342</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>CB-6</t>
+          <t>SE-3</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D283">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Alex's Smoke Shop</t>
+          <t>IGA food world</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>421 Russell Rd, Ashland, Kentucky, 41101</t>
+          <t>3149 Highway 805, Neon, Kentucky, 41840</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>08/28/26</t>
+          <t>09/01/26</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Not Attempted, Permanently Closed</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>SE-4</t>
+          <t>CB-6</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D284">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Cornetts Whiskey Store</t>
+          <t>Alex's Smoke Shop</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>11300 KY-7, Cornettsville, KY 41731</t>
+          <t>421 Russell Rd, Ashland, Kentucky, 41101</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>09/01/26</t>
+          <t>08/28/26</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Not Attempted, Permanently Closed</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10353</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>JS-4</t>
+          <t>SE-4</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D285">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Kroger</t>
+          <t>Cornetts Whiskey Store</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>711 Martin Luther King Jr Blvd, Ste 5, Ashland, Kentucky, 41101</t>
+          <t>11300 KY-7, Cornettsville, KY 41731</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>07/21/26</t>
+          <t>09/01/26</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -23386,7 +23600,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>09/17/26</t>
+          <t>07/21/26</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -23426,7 +23640,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>08/31/26</t>
+          <t>09/17/26</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -23438,35 +23652,35 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>10372</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>NB-2</t>
+          <t>JS-4</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D288">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Super Quik</t>
+          <t>Kroger</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>951 N Carol Malone Blvd, Grayson, Kentucky, 41143</t>
+          <t>711 Martin Luther King Jr Blvd, Ste 5, Ashland, Kentucky, 41101</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>07/22/26</t>
+          <t>08/31/26</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -23478,12 +23692,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>10384</t>
+          <t>10372</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>NB-6</t>
+          <t>NB-2</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -23492,21 +23706,21 @@
         </is>
       </c>
       <c r="D289">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Go Time</t>
+          <t>Super Quik</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>8354 Highway 15 S, Jackson, Kentucky, 41339</t>
+          <t>951 N Carol Malone Blvd, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>07/29/26</t>
+          <t>07/22/26</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -23518,35 +23732,35 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>10400</t>
+          <t>10384</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>CB-2</t>
+          <t>NB-6</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D290">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Go Time</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>27 Chicken Coop Rd, Grayson, Kentucky, 41143</t>
+          <t>8354 Highway 15 S, Jackson, Kentucky, 41339</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>07/20/26</t>
+          <t>07/29/26</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -23558,35 +23772,35 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10400</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>AL-1</t>
+          <t>CB-2</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D291">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Indian Hollow Liquors</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>241 Highway 15 S, Jackson, Kentucky, 41339</t>
+          <t>27 Chicken Coop Rd, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>09/04/26</t>
+          <t>07/20/26</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -23598,35 +23812,35 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>10453</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>NB-4</t>
+          <t>AL-1</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D292">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Clark's Pump-N-Shop</t>
+          <t>Indian Hollow Liquors</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>311 N Carol Malone Blvd, Grayson, Kentucky, 41143</t>
+          <t>241 Highway 15 S, Jackson, Kentucky, 41339</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>07/22/26</t>
+          <t>09/04/26</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -23638,97 +23852,97 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>10458</t>
+          <t>10453</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>SE-2</t>
+          <t>NB-4</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D293">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Southern Spirits Liquor Store</t>
+          <t>Clark's Pump-N-Shop</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>2815 N Main St, Hazard, Kentucky, 41701</t>
+          <t>311 N Carol Malone Blvd, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>07/17/26</t>
+          <t>07/22/26</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Not Attempted, Permanently Closed</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>10476</t>
+          <t>10458</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>AL-3</t>
+          <t>SE-2</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D294">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Super Spirits Wine &amp; Tobacco</t>
+          <t>Southern Spirits Liquor Store</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>197 Combs Rd, Hazard, KY 41701</t>
+          <t>2815 N Main St, Hazard, Kentucky, 41701</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>08/21/26</t>
+          <t>07/17/26</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Not Attempted, Permanently Closed</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>10476</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>CB-6</t>
+          <t>AL-3</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D295">
@@ -23736,17 +23950,17 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>ARCO</t>
+          <t>Super Spirits Wine &amp; Tobacco</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>1805 Main St W, Ashland, KY 41102</t>
+          <t>197 Combs Rd, Hazard, KY 41701</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>08/17/26</t>
+          <t>08/21/26</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -23758,30 +23972,30 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>10486</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>JS-3</t>
+          <t>CB-6</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D296">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Carter Avenue Beverage Center</t>
+          <t>ARCO</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>2441 Carter Ave, Ashland, Kentucky, 41101</t>
+          <t>1805 Main St W, Ashland, KY 41102</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -23798,35 +24012,35 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>10532</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>NB-4</t>
+          <t>JS-3</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D297">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Grayson Tobacco &amp; Vape</t>
+          <t>Carter Avenue Beverage Center</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>501 N Carol Malone Blvd, Grayson, Kentucky, 41143</t>
+          <t>2441 Carter Ave, Ashland, Kentucky, 41101</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>07/29/26</t>
+          <t>08/17/26</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -23838,115 +24052,115 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>10535</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>AL-6</t>
+          <t>NB-4</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D298">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>KC's Puff &amp; Snuff</t>
+          <t>Grayson Tobacco &amp; Vape</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>21226 Highway 421, Hyden, Kentucky, 41749</t>
+          <t>501 N Carol Malone Blvd, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>07/29/26</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Ineligible - Drive Through / Gas Kiosk</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>10561</t>
+          <t>10535</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>SE-7</t>
+          <t>AL-6</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D299">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Fourseam Liquor</t>
+          <t>KC's Puff &amp; Snuff</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>3221 S Ky Highway 15, Hazard, Kentucky, 41701</t>
+          <t>21226 Highway 421, Hyden, Kentucky, 41749</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>09/17/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Ineligible - Drive Through / Gas Kiosk</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>10587</t>
+          <t>10561</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>JS-4</t>
+          <t>SE-7</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D300">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>AM PM Spirits Wine &amp; Tobacco</t>
+          <t>Fourseam Liquor</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>901 13th St, Ashland, Kentucky, 41101</t>
+          <t>3221 S Ky Highway 15, Hazard, Kentucky, 41701</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>08/18/26</t>
+          <t>09/17/26</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -23958,35 +24172,35 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>10587</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>AL-5</t>
+          <t>JS-4</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D301">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>ARCO</t>
+          <t>AM PM Spirits Wine &amp; Tobacco</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>3145 KY-15, Hazard, KY 41701</t>
+          <t>901 13th St, Ashland, Kentucky, 41101</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>09/02/26</t>
+          <t>08/18/26</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -23998,115 +24212,115 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>JS-3</t>
+          <t>AL-5</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D302">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>AAA Liquor</t>
+          <t>ARCO</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>3000 Winchester Ave., Ashland, KY 41101</t>
+          <t>3145 KY-15, Hazard, KY 41701</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>07/13/26</t>
+          <t>09/02/26</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Not Attempted, Permanently Closed</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>10596</t>
+          <t>10595</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>CB-6</t>
+          <t>JS-3</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D303">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Kroger</t>
+          <t>AAA Liquor</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>370 Diedrich Blvd, Ashland KY 41101</t>
+          <t>3000 Winchester Ave., Ashland, KY 41101</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>08/12/26</t>
+          <t>07/13/26</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Not Attempted, Permanently Closed</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>10599</t>
+          <t>10596</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>JS-6</t>
+          <t>CB-6</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D304">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>AM PM Spirits Wine &amp; Tobacco</t>
+          <t>Kroger</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>9411 US 60 Ashland, KY 41102</t>
+          <t>370 Diedrich Blvd, Ashland KY 41101</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>08/24/26</t>
+          <t>08/12/26</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -24118,12 +24332,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>10599</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>JS-2</t>
+          <t>JS-6</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -24132,7 +24346,7 @@
         </is>
       </c>
       <c r="D305">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -24141,12 +24355,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>3500 Court Street, Catlettsburg, KY 41129</t>
+          <t>9411 US 60 Ashland, KY 41102</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>08/24/26</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -24158,12 +24372,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>10601</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>JS-3</t>
+          <t>JS-2</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -24172,21 +24386,21 @@
         </is>
       </c>
       <c r="D306">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Ashland Adult Beverage Center</t>
+          <t>AM PM Spirits Wine &amp; Tobacco</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>948 29th Street Ashland, KY 41101</t>
+          <t>3500 Court Street, Catlettsburg, KY 41129</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>08/29/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -24198,12 +24412,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>JS-5</t>
+          <t>JS-3</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -24212,38 +24426,38 @@
         </is>
       </c>
       <c r="D307">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Boyd Beverage Center</t>
+          <t>Ashland Adult Beverage Center</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>1530 Shopes Creek Road, Ashland, KY 41102</t>
+          <t>948 29th Street Ashland, KY 41101</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>07/13/26</t>
+          <t>08/29/26</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Not Attempted, Permanently Closed</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>JS-1</t>
+          <t>JS-5</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -24252,141 +24466,141 @@
         </is>
       </c>
       <c r="D308">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>1st Stop Liquor</t>
+          <t>Boyd Beverage Center</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>1125 Winchester Avenue, Ashland, KY 41101</t>
+          <t>1530 Shopes Creek Road, Ashland, KY 41102</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>08/17/26</t>
+          <t>07/13/26</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Not Attempted, Permanently Closed</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>10604</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>CB-7</t>
+          <t>JS-1</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D309">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Ashland Beverage Centre</t>
+          <t>1st Stop Liquor</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>1609 Diedrich Blvd, Russell KY 41169</t>
+          <t>1125 Winchester Avenue, Ashland, KY 41101</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>08/17/26</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>JS-6</t>
+          <t>CB-7</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D310">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Good Spirits</t>
+          <t>Ashland Beverage Centre</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>1350 Wolohan Dr, Ashland, KY 41102</t>
+          <t>1609 Diedrich Blvd, Russell KY 41169</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>08/24/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>10608</t>
+          <t>10605</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>AL-4</t>
+          <t>JS-6</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D311">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Sunoco</t>
+          <t>Good Spirits</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>1366 Combs Rd, Hazard, Kentucky, 41701</t>
+          <t>1350 Wolohan Dr, Ashland, KY 41102</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>08/21/26</t>
+          <t>08/24/26</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -24398,35 +24612,35 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>10608</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>SE-5</t>
+          <t>AL-4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D312">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Whitesburg Tobacco Shed</t>
+          <t>Sunoco</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>136 Parkway Plaza Loop, Whitesburg, Kentucky, 41858</t>
+          <t>1366 Combs Rd, Hazard, Kentucky, 41701</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>08/14/26</t>
+          <t>08/21/26</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -24438,35 +24652,35 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>10610</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>NB-3</t>
+          <t>SE-5</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D313">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Dionysus Beverage Sales</t>
+          <t>Whitesburg Tobacco Shed</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>221 National Ave, Grayson, Kentucky, 41143</t>
+          <t>136 Parkway Plaza Loop, Whitesburg, Kentucky, 41858</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>07/23/26</t>
+          <t>08/14/26</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -24478,35 +24692,35 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>10611</t>
+          <t>10610</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>CB-1</t>
+          <t>NB-3</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D314">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>AM PM Liquor &amp; Tobacco</t>
+          <t>Dionysus Beverage Sales</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>46 Depot Dr, South Shore, Kentucky, 41175</t>
+          <t>221 National Ave, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>07/28/26</t>
+          <t>07/23/26</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -24518,12 +24732,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>10611</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>CB-3</t>
+          <t>CB-1</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -24532,21 +24746,21 @@
         </is>
       </c>
       <c r="D315">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Greenup Mart</t>
+          <t>AM PM Liquor &amp; Tobacco</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>1522 Seaton Ave, Greenup, Kentucky, 41144</t>
+          <t>46 Depot Dr, South Shore, Kentucky, 41175</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>08/24/26</t>
+          <t>07/28/26</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -24558,35 +24772,35 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>JS-4</t>
+          <t>CB-3</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D316">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Good Spirits</t>
+          <t>Greenup Mart</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>1117 13th St, Ashland, Kentucky, 41101</t>
+          <t>1522 Seaton Ave, Greenup, Kentucky, 41144</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>08/18/26</t>
+          <t>08/24/26</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -24598,21 +24812,21 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>10615</t>
+          <t>10614</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>CB-3</t>
+          <t>JS-4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D317">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -24621,12 +24835,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>102 Lil Way, Greenup, Kentucky, 41144</t>
+          <t>1117 13th St, Ashland, Kentucky, 41101</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>08/19/26</t>
+          <t>08/18/26</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -24638,7 +24852,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>10616</t>
+          <t>10615</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -24652,7 +24866,7 @@
         </is>
       </c>
       <c r="D318">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -24661,7 +24875,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>950 Townhill Plz, Greenup, Kentucky, 41144</t>
+          <t>102 Lil Way, Greenup, Kentucky, 41144</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -24671,82 +24885,82 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Not Attempted, Permanently Closed</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>10616</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>JS-7</t>
+          <t>CB-3</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D319">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Mud Slingers</t>
+          <t>Good Spirits</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>14778 State Route 854, Rush, Kentucky, 41168</t>
+          <t>950 Townhill Plz, Greenup, Kentucky, 41144</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>07/30/26</t>
+          <t>08/19/26</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Not Attempted, Permanently Closed</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>10632</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>SE-3</t>
+          <t>JS-7</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D320">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Fast Track #5</t>
+          <t>Mud Slingers</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>3668 Highway 582, Pine Top, Kentucky, 41843</t>
+          <t>14778 State Route 854, Rush, Kentucky, 41168</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>09/01/26</t>
+          <t>07/30/26</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -24758,12 +24972,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>SE-4</t>
+          <t>SE-3</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -24772,38 +24986,38 @@
         </is>
       </c>
       <c r="D321">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Wildcats Country Market</t>
+          <t>Fast Track #5</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>8649 KY Highway 7, Viper, Kentucky, 41774</t>
+          <t>3668 Highway 582, Pine Top, Kentucky, 41843</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>07/29/26</t>
+          <t>09/01/26</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Not Attempted, Permanently Closed</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>10639</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>SE-7</t>
+          <t>SE-4</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -24812,91 +25026,101 @@
         </is>
       </c>
       <c r="D322">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Wildcats Country Market</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>317 Happy Cir, Happy, Kentucky, 41746</t>
+          <t>8649 KY Highway 7, Viper, Kentucky, 41774</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>07/16/26</t>
+          <t>07/29/26</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Not Attempted, Permanently Closed</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>10642</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>AL-1</t>
+          <t>SE-7</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D323">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>DG Market</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>59 Highway 15 N, Jackson, Kentucky, 41339</t>
+          <t>317 Happy Cir, Happy, Kentucky, 41746</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>07/16/26</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>10643</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>CB-6</t>
+          <t>AL-1</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D324">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>DG Market</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>259 Wheatley Rd, Ashland, Kentucky, 41101</t>
+          <t>59 Highway 15 N, Jackson, Kentucky, 41339</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>08/17/26</t>
+          <t>10/06/26</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -24908,21 +25132,21 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>10646</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>NB-6</t>
+          <t>CB-6</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D325">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -24931,12 +25155,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>10349 Highway 15 S, Lost Creek, Kentucky, 41348</t>
+          <t>259 Wheatley Rd, Ashland, Kentucky, 41101</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>07/21/26</t>
+          <t>08/17/26</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -24948,12 +25172,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>10647</t>
+          <t>10646</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>NB-5</t>
+          <t>NB-6</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -24962,21 +25186,21 @@
         </is>
       </c>
       <c r="D326">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Grayson Beverage Center</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>126 Interstate Dr, Grayson, Kentucky, 41143</t>
+          <t>10349 Highway 15 S, Lost Creek, Kentucky, 41348</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>08/21/26</t>
+          <t>07/21/26</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -24988,12 +25212,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>10647</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>NB-4</t>
+          <t>NB-5</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -25002,16 +25226,16 @@
         </is>
       </c>
       <c r="D327">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Smoker Friendly</t>
+          <t>Grayson Beverage Center</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>517 E Main St, Grayson, Kentucky, 41143</t>
+          <t>126 Interstate Dr, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -25068,132 +25292,132 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>10649</t>
+          <t>10648</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>CB-4</t>
+          <t>NB-4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D329">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Sams Carryout</t>
+          <t>Smoker Friendly</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>715 Greenup Ave, Russell, Kentucky, 41169</t>
+          <t>517 E Main St, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>08/21/26</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>SE-1</t>
+          <t>CB-4</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D330">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Fast Track</t>
+          <t>Sams Carryout</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>104 Highway 899, Hindman, Kentucky, 41822</t>
+          <t>715 Greenup Ave, Russell, Kentucky, 41169</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>10/01/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Eligible, Asked to Leave Before Audit Started - Permission Not Given</t>
+          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>10651</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>AL-6</t>
+          <t>SE-1</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D331">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Mountain Liquor</t>
+          <t>Fast Track</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>21400 US-421, Hyden, KY 41749</t>
+          <t>104 Highway 899, Hindman, Kentucky, 41822</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>10/01/26</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Eligible, Asked to Leave Before Audit Started - Permission Not Given</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>10653</t>
+          <t>10651</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>AL-3</t>
+          <t>AL-6</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -25202,21 +25426,21 @@
         </is>
       </c>
       <c r="D332">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Brewers Liquors</t>
+          <t>Mountain Liquor</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>611 Memorial Dr, Hazard, Kentucky, 41701</t>
+          <t>21400 US-421, Hyden, KY 41749</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>07/29/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -25228,12 +25452,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>10655</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>AL-5</t>
+          <t>AL-3</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -25242,21 +25466,21 @@
         </is>
       </c>
       <c r="D333">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>56 Wine &amp; Spirits</t>
+          <t>Brewers Liquors</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>3256 W KY Highway 80, Hazard, Kentucky, 41701</t>
+          <t>611 Memorial Dr, Hazard, Kentucky, 41701</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>09/01/26</t>
+          <t>07/29/26</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -25268,35 +25492,35 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10655</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>SE-2</t>
+          <t>AL-5</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D334">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Go Time</t>
+          <t>56 Wine &amp; Spirits</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>32 Constitution Ave, Hazard, KY 41701</t>
+          <t>3256 W KY Highway 80, Hazard, Kentucky, 41701</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>08/26/26</t>
+          <t>09/01/26</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -25308,35 +25532,35 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>10656</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>AL-4</t>
+          <t>SE-2</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D335">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Top of the Hill Liquors LLC</t>
+          <t>Go Time</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>33 Boone Ridge Rd, Hazard, Kentucky, 41701</t>
+          <t>32 Constitution Ave, Hazard, KY 41701</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>09/24/26</t>
+          <t>08/26/26</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -25348,35 +25572,35 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>10658</t>
+          <t>10657</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>CB-4</t>
+          <t>AL-4</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D336">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>DG Market</t>
+          <t>Top of the Hill Liquors LLC</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>652 Heaberlin Rd, Greenup, Kentucky, 41144</t>
+          <t>33 Boone Ridge Rd, Hazard, Kentucky, 41701</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>07/23/26</t>
+          <t>09/24/26</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -25388,12 +25612,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>CB-7</t>
+          <t>CB-4</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -25402,21 +25626,21 @@
         </is>
       </c>
       <c r="D337">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>DG Market</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>4501 State Route 2, Greenup, Kentucky, 41144</t>
+          <t>652 Heaberlin Rd, Greenup, Kentucky, 41144</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>07/20/26</t>
+          <t>07/23/26</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -25428,35 +25652,35 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>SE-4</t>
+          <t>CB-7</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D338">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Soggy Bottom General Store</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>83 Left Fork Maces Creek Rd, Viper, Kentucky, 41774</t>
+          <t>4501 State Route 2, Greenup, Kentucky, 41144</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>07/29/26</t>
+          <t>07/20/26</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -25468,7 +25692,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>10661</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -25482,16 +25706,16 @@
         </is>
       </c>
       <c r="D339">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>The Front Porch 2</t>
+          <t>Soggy Bottom General Store</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>35 KY Highway 463, Slemp, Kentucky, 41763</t>
+          <t>83 Left Fork Maces Creek Rd, Viper, Kentucky, 41774</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -25508,12 +25732,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>10661</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>SE-2</t>
+          <t>SE-4</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -25522,21 +25746,21 @@
         </is>
       </c>
       <c r="D340">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>The Moon Spirits</t>
+          <t>The Front Porch 2</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>388 Highway 80 E, Hindman, Kentucky, 41822</t>
+          <t>35 KY Highway 463, Slemp, Kentucky, 41763</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>10/01/26</t>
+          <t>07/29/26</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -25548,12 +25772,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10662</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>SE-4</t>
+          <t>SE-2</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -25562,21 +25786,21 @@
         </is>
       </c>
       <c r="D341">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Viper Hardware</t>
+          <t>The Moon Spirits</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>8728 KY Highway 7, Viper, Kentucky, 41774</t>
+          <t>388 Highway 80 E, Hindman, Kentucky, 41822</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>09/17/26</t>
+          <t>10/01/26</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -25588,35 +25812,35 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>NB-1</t>
+          <t>SE-4</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D342">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>AM PM Spirits Wine &amp; Tobacco</t>
+          <t>Viper Hardware</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>131 Jessica Ln, Suite E, Olive Hill, KY 41164</t>
+          <t>8728 KY Highway 7, Viper, Kentucky, 41774</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>07/30/26</t>
+          <t>09/17/26</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -25628,12 +25852,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>10665</t>
+          <t>10664</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>NB-3</t>
+          <t>NB-1</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -25642,21 +25866,21 @@
         </is>
       </c>
       <c r="D343">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>T &amp; T Outdoors</t>
+          <t>AM PM Spirits Wine &amp; Tobacco</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>4609 S State Highway 7, Grayson, Kentucky, 41143</t>
+          <t>131 Jessica Ln, Suite E, Olive Hill, KY 41164</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>07/23/26</t>
+          <t>07/30/26</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -25668,35 +25892,35 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>10666</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>CB-1</t>
+          <t>NB-3</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D344">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Jenny's Mart</t>
+          <t>T &amp; T Outdoors</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>1337 KY-8, South Portsmouth, KY 41174</t>
+          <t>4609 S State Highway 7, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>07/28/26</t>
+          <t>07/23/26</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -25708,132 +25932,132 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>10667</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>JS-2</t>
+          <t>CB-1</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D345">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Cigarette Outlet</t>
+          <t>Jenny's Mart</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>308 35th St, Catlettsburg, Kentucky, 41129</t>
+          <t>1337 KY-8, South Portsmouth, KY 41174</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>08/27/26</t>
+          <t>07/28/26</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>10668</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>CB-5</t>
+          <t>JS-2</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D346">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goodfell's Tobacco Store </t>
+          <t>Cigarette Outlet</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>2002 Argillite Rd, Flatwoods, Kentucky, 41139</t>
+          <t>308 35th St, Catlettsburg, Kentucky, 41129</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>07/23/26</t>
+          <t>08/27/26</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Not Attempted, Permanently Closed</t>
+          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>10669</t>
+          <t>10668</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>JS-5</t>
+          <t>CB-5</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D347">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Fat Ash Cigar Lounge</t>
+          <t xml:space="preserve">Goodfell's Tobacco Store </t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>8110 US Route 60, Ashland, Kentucky, 41102</t>
+          <t>2002 Argillite Rd, Flatwoods, Kentucky, 41139</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>07/13/26</t>
+          <t>07/23/26</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Not Attempted, Permanently Closed</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10669</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>JS-1</t>
+          <t>JS-5</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -25842,16 +26066,16 @@
         </is>
       </c>
       <c r="D348">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Phoenix Vapors</t>
+          <t>Fat Ash Cigar Lounge</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>222 16th St, Ashland, Kentucky, 41101</t>
+          <t>8110 US Route 60, Ashland, Kentucky, 41102</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -25861,79 +26085,119 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
+          <t>Eligible, Audit Completed</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>10670</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>NB-4</t>
+          <t>JS-1</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D349">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Tobacco Barn</t>
+          <t>Phoenix Vapors</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>521 E Main St, Grayson, Kentucky, 41143</t>
+          <t>222 16th St, Ashland, Kentucky, 41101</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>08/21/26</t>
+          <t>07/13/26</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Not Attempted, Permanently Closed</t>
+          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>New_Store999</t>
+          <t>10671</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>NB-4</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D350">
+        <v>3</v>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Tobacco Barn</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>521 E Main St, Grayson, Kentucky, 41143</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>10/04/26</t>
+          <t>08/21/26</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Eligible, Audit Completed</t>
+          <t>Not Attempted, Permanently Closed</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
+          <t>New_Store999</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>10/04/26</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
           <t>T_Store999</t>
         </is>
       </c>
-      <c r="G351" t="inlineStr">
+      <c r="G352" t="inlineStr">
         <is>
           <t>07/22/26</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr">
+      <c r="H352" t="inlineStr">
         <is>
           <t>Ineligible - Drive Through / Gas Kiosk</t>
         </is>
@@ -25946,7 +26210,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -25984,12 +26248,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10642</t>
+          <t>10097</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AL-1</t>
+          <t>AL-3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -25998,28 +26262,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DG Market</t>
+          <t>Fast Lane Discount Tobacco</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>59 Highway 15 N, Jackson, Kentucky, 41339</t>
+          <t>373 Main St, Hazard, Kentucky, 41701</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>10094</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AL-3</t>
+          <t>AL-4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -26028,28 +26292,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fast Lane Discount Tobacco</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>373 Main St, Hazard, Kentucky, 41701</t>
+          <t>400 Village Ln, Hazard, Kentucky, 41701</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10094</t>
+          <t>10138</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AL-4</t>
+          <t>AL-6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -26058,53 +26322,53 @@
         </is>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>400 Village Ln, Hazard, Kentucky, 41701</t>
+          <t>21287 Highway 421, Hyden, Kentucky, 41749</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AL-6</t>
+          <t>CB-4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21287 Highway 421, Hyden, Kentucky, 41749</t>
+          <t>8380 US-23 N, Russell, Kentucky, 41169</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10025</t>
+          <t>10161</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -26118,33 +26382,33 @@
         </is>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>Strictly Tobacco</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8380 US-23 N, Russell, Kentucky, 41169</t>
+          <t>1700 US Hwy 23, Russell, Kentucky, 41169</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>10279</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CB-4</t>
+          <t>JS-6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="D7">
@@ -26152,29 +26416,29 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Strictly Tobacco</t>
+          <t>Marathon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1700 US Hwy 23, Russell, Kentucky, 41169</t>
+          <t>2100 State Route 3, Catlettsburg, Kentucky, 41129</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10279</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JS-6</t>
+          <t>NB-5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="D8">
@@ -26182,102 +26446,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Marathon</t>
+          <t>Loves Travel Stop</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2100 State Route 3, Catlettsburg, Kentucky, 41129</t>
+          <t>750 N Carol Malone Blvd, Grayson, Kentucky, 41143</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>10218</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NB-5</t>
+          <t>SE-1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Loves Travel Stop</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>750 N Carol Malone Blvd, Grayson, Kentucky, 41143</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>10218</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SE-1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>7</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Walgreens</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
           <t>100 Holly Hills Mall Rd, Hindman, Kentucky, 41822</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10208</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SE-4</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Shell</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>108 E Main St, Hazard, Kentucky, 41701</t>
         </is>
       </c>
     </row>
